--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5800</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>6400</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -833,72 +836,75 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>6900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4800</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>3800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19700</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>11700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E9" s="3">
         <v>4900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1800</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1700</v>
       </c>
       <c r="I9" s="3">
         <v>1700</v>
@@ -907,90 +913,93 @@
         <v>1700</v>
       </c>
       <c r="K9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L9" s="3">
         <v>1800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-1700</v>
       </c>
       <c r="I10" s="3">
         <v>-1700</v>
@@ -999,73 +1008,76 @@
         <v>-1700</v>
       </c>
       <c r="K10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L10" s="3">
         <v>-1800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-2400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E12" s="3">
         <v>9900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>600</v>
       </c>
       <c r="O12" s="3">
         <v>600</v>
       </c>
       <c r="P12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>1100</v>
       </c>
       <c r="AE12" s="3">
         <v>1100</v>
       </c>
       <c r="AF12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1308,17 +1327,17 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-900</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
@@ -1332,14 +1351,14 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
@@ -1356,8 +1375,8 @@
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1365,17 +1384,20 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3">
         <v>16100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,82 +1747,83 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>300</v>
       </c>
       <c r="T20" s="3">
+        <v>300</v>
+      </c>
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>3500</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>-100</v>
@@ -1802,105 +1835,111 @@
         <v>-100</v>
       </c>
       <c r="AE20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1913,14 +1952,14 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
@@ -1947,10 +1986,10 @@
         <v>200</v>
       </c>
       <c r="R22" s="3">
+        <v>200</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
@@ -1968,7 +2007,7 @@
         <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>300</v>
@@ -1980,7 +2019,7 @@
         <v>300</v>
       </c>
       <c r="AC22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AD22" s="3">
         <v>400</v>
@@ -1989,102 +2028,108 @@
         <v>400</v>
       </c>
       <c r="AF22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2151,17 +2196,17 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>10</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3" t="s">
+      <c r="AA24" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>10</v>
@@ -2169,14 +2214,17 @@
       <c r="AD24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3" t="s">
+      <c r="AE24" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,82 +2885,85 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-300</v>
       </c>
       <c r="T32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>100</v>
@@ -2906,105 +2975,111 @@
         <v>100</v>
       </c>
       <c r="AE32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E41" s="3">
         <v>54600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>77300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>39900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3488,39 +3577,39 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>10200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1300</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
@@ -3536,17 +3625,20 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>5600</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
@@ -3590,11 +3682,11 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>1100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
@@ -3608,17 +3700,17 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>7900</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
@@ -3626,33 +3718,36 @@
         <v>0</v>
       </c>
       <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E44" s="3">
         <v>4700</v>
-      </c>
-      <c r="E44" s="3">
-        <v>6300</v>
       </c>
       <c r="F44" s="3">
         <v>6300</v>
       </c>
       <c r="G44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="H44" s="3">
         <v>9900</v>
       </c>
       <c r="I44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J44" s="3">
         <v>7900</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>10</v>
@@ -3669,266 +3764,275 @@
       <c r="O44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="3">
         <v>7600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>300</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
       <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
         <v>7100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1800</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
       <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
         <v>7000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1200</v>
       </c>
       <c r="F45" s="3">
         <v>1200</v>
       </c>
       <c r="G45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1100</v>
       </c>
       <c r="U45" s="3">
         <v>1100</v>
       </c>
       <c r="V45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="W45" s="3">
         <v>800</v>
       </c>
       <c r="X45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E46" s="3">
         <v>66500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>75500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>84800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>53900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3963,11 +4067,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="W47" s="3">
-        <v>7500</v>
       </c>
       <c r="X47" s="3">
         <v>7500</v>
@@ -3979,7 +4083,7 @@
         <v>7500</v>
       </c>
       <c r="AA47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AB47" s="3">
         <v>7600</v>
@@ -3996,100 +4100,106 @@
       <c r="AF47" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E48" s="3">
         <v>56100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>56100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>55600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>56300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>56800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>60100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>61100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>63500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>64800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>65800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>66800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>67800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>68900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>69900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>71000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>69000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>69900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>70800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>71600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>72700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>74300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>75200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>75900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,79 +4480,82 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E52" s="3">
         <v>8400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>8100</v>
       </c>
       <c r="H52" s="3">
         <v>8100</v>
       </c>
       <c r="I52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J52" s="3">
         <v>8000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>15900</v>
       </c>
       <c r="K52" s="3">
         <v>15900</v>
       </c>
       <c r="L52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="M52" s="3">
         <v>15800</v>
       </c>
       <c r="N52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="O52" s="3">
         <v>15700</v>
       </c>
       <c r="P52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>7900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9800</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>10</v>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E54" s="3">
         <v>131100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>139600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>149100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>107700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>81800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>86600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>86300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>86900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>90400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>88200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>93100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>97100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>101300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>95400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>88400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>92800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>97400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>98000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>89900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,61 +4837,62 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1400</v>
       </c>
       <c r="J57" s="3">
         <v>1400</v>
       </c>
       <c r="K57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
       </c>
       <c r="O57" s="3">
         <v>400</v>
       </c>
       <c r="P57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
-      </c>
-      <c r="T57" s="3">
-        <v>600</v>
       </c>
       <c r="U57" s="3">
         <v>600</v>
@@ -4774,34 +4904,37 @@
         <v>600</v>
       </c>
       <c r="X57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4818,43 +4951,43 @@
         <v>5400</v>
       </c>
       <c r="H58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I58" s="3">
         <v>5300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>500</v>
       </c>
       <c r="Q58" s="3">
+        <v>500</v>
+      </c>
+      <c r="R58" s="3">
         <v>1700</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="S58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>5200</v>
@@ -4863,327 +4996,339 @@
         <v>5200</v>
       </c>
       <c r="W58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="X58" s="3">
         <v>5100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4900</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>4800</v>
       </c>
       <c r="AA58" s="3">
         <v>4800</v>
       </c>
       <c r="AB58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>4600</v>
       </c>
       <c r="AD58" s="3">
         <v>4600</v>
       </c>
       <c r="AE58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AF58" s="3">
         <v>4500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3600</v>
+        <v>2700</v>
       </c>
       <c r="E59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1800</v>
       </c>
       <c r="S59" s="3">
         <v>1800</v>
       </c>
       <c r="T59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="U59" s="3">
         <v>1900</v>
       </c>
       <c r="V59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W59" s="3">
         <v>3100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>8600</v>
       </c>
       <c r="I60" s="3">
         <v>8600</v>
       </c>
       <c r="J60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K60" s="3">
         <v>9300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>2300</v>
       </c>
       <c r="S60" s="3">
         <v>2300</v>
       </c>
       <c r="T60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U60" s="3">
         <v>7800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>3200</v>
+        <v>1500</v>
       </c>
       <c r="F61" s="3">
-        <v>4600</v>
+        <v>2900</v>
       </c>
       <c r="G61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H61" s="3">
         <v>5700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>12300</v>
       </c>
       <c r="M61" s="3">
         <v>12300</v>
       </c>
       <c r="N61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="O61" s="3">
         <v>12400</v>
-      </c>
-      <c r="O61" s="3">
-        <v>12700</v>
       </c>
       <c r="P61" s="3">
         <v>12700</v>
       </c>
       <c r="Q61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="R61" s="3">
         <v>11500</v>
-      </c>
-      <c r="R61" s="3">
-        <v>12200</v>
       </c>
       <c r="S61" s="3">
         <v>12200</v>
       </c>
       <c r="T61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="U61" s="3">
         <v>7000</v>
       </c>
       <c r="V61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W61" s="3">
         <v>8300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>19400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>44200</v>
+        <v>43500</v>
       </c>
       <c r="E62" s="3">
-        <v>38900</v>
+        <v>44700</v>
       </c>
       <c r="F62" s="3">
-        <v>39100</v>
+        <v>39200</v>
       </c>
       <c r="G62" s="3">
-        <v>33100</v>
+        <v>39400</v>
       </c>
       <c r="H62" s="3">
         <v>33100</v>
@@ -5192,76 +5337,79 @@
         <v>33100</v>
       </c>
       <c r="J62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="K62" s="3">
         <v>36200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>36200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>31400</v>
-      </c>
-      <c r="P62" s="3">
-        <v>31800</v>
       </c>
       <c r="Q62" s="3">
         <v>31800</v>
       </c>
       <c r="R62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="S62" s="3">
         <v>31500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>31600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>31500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>32400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>32100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>31400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>29100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>26900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>27100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>26800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E66" s="3">
         <v>57900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53900</v>
-      </c>
-      <c r="O66" s="3">
-        <v>47700</v>
       </c>
       <c r="P66" s="3">
         <v>47700</v>
       </c>
       <c r="Q66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="R66" s="3">
         <v>47300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>46100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>47100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>49400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>49900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>49600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>51000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>52700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>54900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-250900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-245400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-228300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-221000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-220300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-215400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-210400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-210000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-203100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-203500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-194400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-187500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-180200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-175000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-171300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-169000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-165400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-167500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-163300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-161300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-157000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-155300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-151500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E76" s="3">
         <v>73200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>89400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>96600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>62500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>66600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>65200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>69400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>51900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>38900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>39000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>42000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>51800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>53400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>48400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>45500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>38800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>41900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>44700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>43100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,13 +7002,14 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
@@ -6820,10 +7018,10 @@
         <v>800</v>
       </c>
       <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
         <v>700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
@@ -6832,7 +7030,7 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L83" s="3">
         <v>1000</v>
@@ -6847,7 +7045,7 @@
         <v>1000</v>
       </c>
       <c r="P83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Q83" s="3">
         <v>1100</v>
@@ -6868,7 +7066,7 @@
         <v>1100</v>
       </c>
       <c r="W83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="X83" s="3">
         <v>900</v>
@@ -6880,10 +7078,10 @@
         <v>900</v>
       </c>
       <c r="AA83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>1300</v>
       </c>
       <c r="AC83" s="3">
         <v>1300</v>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,46 +7702,47 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>10</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7570,13 +7790,16 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,38 +7985,41 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -7810,17 +8039,17 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -7828,31 +8057,34 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>3500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,56 +8495,59 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8310,43 +8555,46 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8363,13 +8611,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-100</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8387,11 +8635,11 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
@@ -8408,11 +8656,11 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -8435,98 +8683,104 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1500</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,161 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
         <v>5400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5800</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>6400</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -839,75 +843,78 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>6900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4800</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>3800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>19700</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
         <v>11700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E9" s="3">
         <v>5100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1700</v>
       </c>
       <c r="J9" s="3">
         <v>1700</v>
@@ -916,93 +923,96 @@
         <v>1700</v>
       </c>
       <c r="L9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M9" s="3">
         <v>1800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-3000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-1700</v>
       </c>
       <c r="J10" s="3">
         <v>-1700</v>
@@ -1011,73 +1021,76 @@
         <v>-1700</v>
       </c>
       <c r="L10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M10" s="3">
         <v>-1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-2400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E12" s="3">
         <v>7200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>600</v>
       </c>
       <c r="P12" s="3">
         <v>600</v>
       </c>
       <c r="Q12" s="3">
+        <v>600</v>
+      </c>
+      <c r="R12" s="3">
         <v>800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>1100</v>
       </c>
       <c r="AF12" s="3">
         <v>1100</v>
       </c>
       <c r="AG12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1330,17 +1350,17 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-900</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
@@ -1354,14 +1374,14 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
@@ -1378,8 +1398,8 @@
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1387,17 +1407,20 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E17" s="3">
         <v>13800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,85 +1781,86 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>300</v>
       </c>
       <c r="T20" s="3">
         <v>300</v>
       </c>
       <c r="U20" s="3">
+        <v>300</v>
+      </c>
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>3500</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>-100</v>
@@ -1838,108 +1872,114 @@
         <v>-100</v>
       </c>
       <c r="AF20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1955,14 +1995,14 @@
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
@@ -1989,10 +2029,10 @@
         <v>200</v>
       </c>
       <c r="S22" s="3">
+        <v>200</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -2010,7 +2050,7 @@
         <v>200</v>
       </c>
       <c r="Z22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>300</v>
@@ -2022,7 +2062,7 @@
         <v>300</v>
       </c>
       <c r="AD22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AE22" s="3">
         <v>400</v>
@@ -2031,105 +2071,111 @@
         <v>400</v>
       </c>
       <c r="AG22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2199,17 +2245,17 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>10</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3" t="s">
+      <c r="AB24" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>10</v>
@@ -2217,14 +2263,17 @@
       <c r="AE24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3" t="s">
+      <c r="AF24" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,85 +2955,88 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-300</v>
       </c>
       <c r="T32" s="3">
         <v>-300</v>
       </c>
       <c r="U32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>100</v>
@@ -2978,108 +3048,114 @@
         <v>100</v>
       </c>
       <c r="AF32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E41" s="3">
         <v>59700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3580,39 +3670,39 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3" t="s">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1300</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3637,11 +3730,11 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>5600</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
       <c r="G43" s="3">
         <v>0</v>
       </c>
@@ -3685,11 +3778,11 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
@@ -3703,17 +3796,17 @@
         <v>0</v>
       </c>
       <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3">
         <v>100</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>7900</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
@@ -3721,36 +3814,39 @@
         <v>0</v>
       </c>
       <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>6300</v>
       </c>
       <c r="G44" s="3">
         <v>6300</v>
       </c>
       <c r="H44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="I44" s="3">
         <v>9900</v>
       </c>
       <c r="J44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K44" s="3">
         <v>7900</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>10</v>
@@ -3767,59 +3863,62 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R44" s="3">
         <v>7600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>300</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
       <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
         <v>7100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1800</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
       <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
         <v>7000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>7500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3827,197 +3926,203 @@
         <v>1300</v>
       </c>
       <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1200</v>
       </c>
       <c r="G45" s="3">
         <v>1200</v>
       </c>
       <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
-      </c>
-      <c r="U45" s="3">
-        <v>1100</v>
       </c>
       <c r="V45" s="3">
         <v>1100</v>
       </c>
       <c r="W45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="X45" s="3">
         <v>800</v>
       </c>
       <c r="Y45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E46" s="3">
         <v>63700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>66500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>84800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>43900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>53900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>48600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>10</v>
+      <c r="E47" s="3">
+        <v>200</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>10</v>
@@ -4034,8 +4139,8 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4070,11 +4175,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="X47" s="3">
-        <v>7500</v>
       </c>
       <c r="Y47" s="3">
         <v>7500</v>
@@ -4086,7 +4191,7 @@
         <v>7500</v>
       </c>
       <c r="AB47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AC47" s="3">
         <v>7600</v>
@@ -4103,103 +4208,109 @@
       <c r="AG47" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E48" s="3">
         <v>56000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>56100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>56100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>56800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>60100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>61100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>63500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>64800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>65800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>66800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>67800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>68900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>69900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>71000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>69000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>69900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>70800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>71600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>72700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>74300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>75200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>75900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,82 +4600,85 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E52" s="3">
         <v>8500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>8100</v>
       </c>
       <c r="I52" s="3">
         <v>8100</v>
       </c>
       <c r="J52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K52" s="3">
         <v>8000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>15900</v>
       </c>
       <c r="L52" s="3">
         <v>15900</v>
       </c>
       <c r="M52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="N52" s="3">
         <v>15800</v>
       </c>
       <c r="O52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="P52" s="3">
         <v>15700</v>
       </c>
       <c r="Q52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="R52" s="3">
         <v>7900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9800</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>10</v>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E54" s="3">
         <v>128400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>131100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>139600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>149100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>107900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>107700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>81800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>86600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>86300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>86900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>90400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>88200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>93100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>97100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>100400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>101300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>95600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>95400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>88400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>92800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>97400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>98000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>89900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,64 +4968,65 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1400</v>
       </c>
       <c r="K57" s="3">
         <v>1400</v>
       </c>
       <c r="L57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
-      </c>
-      <c r="O57" s="3">
-        <v>400</v>
       </c>
       <c r="P57" s="3">
         <v>400</v>
       </c>
       <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>600</v>
       </c>
       <c r="V57" s="3">
         <v>600</v>
@@ -4907,90 +5038,93 @@
         <v>600</v>
       </c>
       <c r="Y57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>5700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5400</v>
       </c>
       <c r="H58" s="3">
         <v>5400</v>
       </c>
       <c r="I58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J58" s="3">
         <v>5300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>800</v>
-      </c>
-      <c r="P58" s="3">
-        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>500</v>
       </c>
       <c r="R58" s="3">
+        <v>500</v>
+      </c>
+      <c r="S58" s="3">
         <v>1700</v>
       </c>
-      <c r="S58" s="3" t="s">
+      <c r="T58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>5200</v>
@@ -4999,227 +5133,236 @@
         <v>5200</v>
       </c>
       <c r="X58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Y58" s="3">
         <v>5100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>4800</v>
       </c>
       <c r="AB58" s="3">
         <v>4800</v>
       </c>
       <c r="AC58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>4600</v>
       </c>
       <c r="AE58" s="3">
         <v>4600</v>
       </c>
       <c r="AF58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AG58" s="3">
         <v>4500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1800</v>
       </c>
       <c r="T59" s="3">
         <v>1800</v>
       </c>
       <c r="U59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="V59" s="3">
         <v>1900</v>
       </c>
       <c r="W59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X59" s="3">
         <v>3100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E60" s="3">
         <v>10000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>8600</v>
       </c>
       <c r="J60" s="3">
         <v>8600</v>
       </c>
       <c r="K60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="L60" s="3">
         <v>9300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>2300</v>
       </c>
       <c r="T60" s="3">
         <v>2300</v>
       </c>
       <c r="U60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V60" s="3">
         <v>7800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5227,111 +5370,114 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>1500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>12300</v>
       </c>
       <c r="N61" s="3">
         <v>12300</v>
       </c>
       <c r="O61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="P61" s="3">
         <v>12400</v>
-      </c>
-      <c r="P61" s="3">
-        <v>12700</v>
       </c>
       <c r="Q61" s="3">
         <v>12700</v>
       </c>
       <c r="R61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="S61" s="3">
         <v>11500</v>
-      </c>
-      <c r="S61" s="3">
-        <v>12200</v>
       </c>
       <c r="T61" s="3">
         <v>12200</v>
       </c>
       <c r="U61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="V61" s="3">
         <v>7000</v>
       </c>
       <c r="W61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X61" s="3">
         <v>8300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>17100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>18300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>19400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E62" s="3">
         <v>43500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>44700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>33100</v>
       </c>
       <c r="I62" s="3">
         <v>33100</v>
@@ -5340,76 +5486,79 @@
         <v>33100</v>
       </c>
       <c r="K62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="L62" s="3">
         <v>36200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>36200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>31400</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>31800</v>
       </c>
       <c r="R62" s="3">
         <v>31800</v>
       </c>
       <c r="S62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="T62" s="3">
         <v>31500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>31600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>31500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>32400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>32100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>31400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>29100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>27000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>26900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>27100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E66" s="3">
         <v>53500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>50100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53900</v>
-      </c>
-      <c r="P66" s="3">
-        <v>47700</v>
       </c>
       <c r="Q66" s="3">
         <v>47700</v>
       </c>
       <c r="R66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="S66" s="3">
         <v>47300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>49400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>49900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>51000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>52700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>54900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-269500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-250900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-245400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-228300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-221000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-220300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-215400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-210400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-210000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-203100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-203500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-194400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-187500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-180200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-175000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-171300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-169000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-165400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-167500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-163300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-161300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-157000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-155300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E76" s="3">
         <v>74900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>73200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>89400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>96600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>66500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>66600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>65200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>69400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>51900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>38900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>39000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>42000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>51800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>53400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>48400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>45500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>38800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>41900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>44700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>43100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7012,7 +7211,7 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
@@ -7021,10 +7220,10 @@
         <v>800</v>
       </c>
       <c r="H83" s="3">
+        <v>800</v>
+      </c>
+      <c r="I83" s="3">
         <v>700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
@@ -7033,7 +7232,7 @@
         <v>800</v>
       </c>
       <c r="L83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="M83" s="3">
         <v>1000</v>
@@ -7048,7 +7247,7 @@
         <v>1000</v>
       </c>
       <c r="Q83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="R83" s="3">
         <v>1100</v>
@@ -7069,7 +7268,7 @@
         <v>1100</v>
       </c>
       <c r="X83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="Y83" s="3">
         <v>900</v>
@@ -7081,10 +7280,10 @@
         <v>900</v>
       </c>
       <c r="AB83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>1300</v>
       </c>
       <c r="AD83" s="3">
         <v>1300</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,49 +7923,50 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>10</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7793,13 +8014,16 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,41 +8215,44 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -8042,17 +8272,17 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -8060,31 +8290,34 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>3500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
       </c>
       <c r="AE94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,59 +8741,62 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E100" s="3">
         <v>5600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>42700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>15400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -8558,43 +8804,46 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8614,13 +8863,13 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8638,11 +8887,11 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -8659,11 +8908,11 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -8686,101 +8935,107 @@
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,168 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
+      <c r="D8" s="3">
+        <v>4700</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>5400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5800</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>6400</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -846,78 +850,81 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>6900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4800</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
       <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19700</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
       <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
         <v>11700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1800</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1700</v>
       </c>
       <c r="K9" s="3">
         <v>1700</v>
@@ -926,96 +933,99 @@
         <v>1700</v>
       </c>
       <c r="M9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N9" s="3">
         <v>1800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
+      <c r="D10" s="3">
+        <v>1400</v>
       </c>
       <c r="E10" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-1700</v>
       </c>
       <c r="K10" s="3">
         <v>-1700</v>
@@ -1024,73 +1034,76 @@
         <v>-1700</v>
       </c>
       <c r="M10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N10" s="3">
         <v>-1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-2400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E12" s="3">
         <v>12500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>600</v>
       </c>
       <c r="Q12" s="3">
         <v>600</v>
       </c>
       <c r="R12" s="3">
+        <v>600</v>
+      </c>
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>1100</v>
       </c>
       <c r="AG12" s="3">
         <v>1100</v>
       </c>
       <c r="AH12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AI12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1353,17 +1373,17 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-900</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
@@ -1377,14 +1397,14 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
@@ -1401,8 +1421,8 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1410,17 +1430,20 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E17" s="3">
         <v>16300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>10</v>
+      <c r="D18" s="3">
+        <v>-11400</v>
       </c>
       <c r="E18" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,88 +1815,89 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>10</v>
+      <c r="D20" s="3">
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>300</v>
       </c>
       <c r="U20" s="3">
         <v>300</v>
       </c>
       <c r="V20" s="3">
+        <v>300</v>
+      </c>
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>3500</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>-100</v>
@@ -1875,111 +1909,117 @@
         <v>-100</v>
       </c>
       <c r="AG20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>10</v>
+      <c r="D21" s="3">
+        <v>-5900</v>
       </c>
       <c r="E21" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1998,14 +2038,14 @@
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
@@ -2032,10 +2072,10 @@
         <v>200</v>
       </c>
       <c r="T22" s="3">
+        <v>200</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
@@ -2053,7 +2093,7 @@
         <v>200</v>
       </c>
       <c r="AA22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB22" s="3">
         <v>300</v>
@@ -2065,7 +2105,7 @@
         <v>300</v>
       </c>
       <c r="AE22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AF22" s="3">
         <v>400</v>
@@ -2074,108 +2114,114 @@
         <v>400</v>
       </c>
       <c r="AH22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2248,17 +2294,17 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>10</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3" t="s">
+      <c r="AC24" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>10</v>
@@ -2266,14 +2312,17 @@
       <c r="AF24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3" t="s">
+      <c r="AG24" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,88 +3025,91 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>10</v>
+      <c r="D32" s="3">
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-300</v>
       </c>
       <c r="U32" s="3">
         <v>-300</v>
       </c>
       <c r="V32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>100</v>
@@ -3051,111 +3121,117 @@
         <v>100</v>
       </c>
       <c r="AG32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E41" s="3">
         <v>53900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>54600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3673,39 +3763,39 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-      <c r="S42" s="3" t="s">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1300</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
@@ -3721,23 +3811,26 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
       </c>
       <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
         <v>5600</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
       <c r="H43" s="3">
         <v>0</v>
       </c>
@@ -3781,11 +3874,11 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
@@ -3799,17 +3892,17 @@
         <v>0</v>
       </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
         <v>7900</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
       <c r="AF43" s="3">
         <v>0</v>
       </c>
@@ -3817,39 +3910,42 @@
         <v>0</v>
       </c>
       <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E44" s="3">
         <v>4700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>6300</v>
       </c>
       <c r="H44" s="3">
         <v>6300</v>
       </c>
       <c r="I44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="J44" s="3">
         <v>9900</v>
       </c>
       <c r="K44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="L44" s="3">
         <v>7900</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>10</v>
@@ -3866,59 +3962,62 @@
       <c r="Q44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S44" s="3">
         <v>7600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>300</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
       <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
         <v>7100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1800</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
-      </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
       <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
         <v>7000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>7500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3929,203 +4028,209 @@
         <v>1300</v>
       </c>
       <c r="F45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G45" s="3">
         <v>1600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1200</v>
       </c>
       <c r="H45" s="3">
         <v>1200</v>
       </c>
       <c r="I45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1100</v>
       </c>
       <c r="W45" s="3">
         <v>1100</v>
       </c>
       <c r="X45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="Y45" s="3">
         <v>800</v>
       </c>
       <c r="Z45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E46" s="3">
         <v>60000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>63700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>66500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>84800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>53900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>48900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E47" s="3">
         <v>200</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="3">
+        <v>200</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -4142,8 +4247,8 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4178,11 +4283,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>7500</v>
       </c>
       <c r="Z47" s="3">
         <v>7500</v>
@@ -4194,7 +4299,7 @@
         <v>7500</v>
       </c>
       <c r="AC47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AD47" s="3">
         <v>7600</v>
@@ -4211,106 +4316,112 @@
       <c r="AH47" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E48" s="3">
         <v>56100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>56100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>56300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>56800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>60100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>63500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>64800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>65800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>66800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>67800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>68900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>69900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>71000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>69000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>69900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>70800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>71600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>72700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>74300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>75200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>75900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,85 +4720,88 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E52" s="3">
         <v>8600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>8100</v>
       </c>
       <c r="J52" s="3">
         <v>8100</v>
       </c>
       <c r="K52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="L52" s="3">
         <v>8000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>15900</v>
       </c>
       <c r="M52" s="3">
         <v>15900</v>
       </c>
       <c r="N52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="O52" s="3">
         <v>15800</v>
       </c>
       <c r="P52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="Q52" s="3">
         <v>15700</v>
       </c>
       <c r="R52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="S52" s="3">
         <v>7900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9800</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>10</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>140600</v>
+      </c>
+      <c r="E54" s="3">
         <v>124900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>128400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>131100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>139600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>149100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>107900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>116800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>86600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>86300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>86900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>90400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>88200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>93100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>97100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>100400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>101300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>95600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>95400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>88400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>92800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>97400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>98000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>89900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,67 +5099,68 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1400</v>
       </c>
       <c r="L57" s="3">
         <v>1400</v>
       </c>
       <c r="M57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
-      </c>
-      <c r="P57" s="3">
-        <v>400</v>
       </c>
       <c r="Q57" s="3">
         <v>400</v>
       </c>
       <c r="R57" s="3">
+        <v>400</v>
+      </c>
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
-      </c>
-      <c r="V57" s="3">
-        <v>600</v>
       </c>
       <c r="W57" s="3">
         <v>600</v>
@@ -5041,34 +5172,37 @@
         <v>600</v>
       </c>
       <c r="Z57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5076,58 +5210,58 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>5700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5400</v>
       </c>
       <c r="I58" s="3">
         <v>5400</v>
       </c>
       <c r="J58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K58" s="3">
         <v>5300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>800</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>500</v>
       </c>
       <c r="R58" s="3">
         <v>500</v>
       </c>
       <c r="S58" s="3">
+        <v>500</v>
+      </c>
+      <c r="T58" s="3">
         <v>1700</v>
       </c>
-      <c r="T58" s="3" t="s">
+      <c r="U58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>5200</v>
@@ -5136,233 +5270,242 @@
         <v>5200</v>
       </c>
       <c r="Y58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Z58" s="3">
         <v>5100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>4800</v>
       </c>
       <c r="AC58" s="3">
         <v>4800</v>
       </c>
       <c r="AD58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>4600</v>
       </c>
       <c r="AF58" s="3">
         <v>4600</v>
       </c>
       <c r="AG58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AH58" s="3">
         <v>4500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1800</v>
       </c>
       <c r="U59" s="3">
         <v>1800</v>
       </c>
       <c r="V59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="W59" s="3">
         <v>1900</v>
       </c>
       <c r="X59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y59" s="3">
         <v>3100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
         <v>5100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>8600</v>
       </c>
       <c r="K60" s="3">
         <v>8600</v>
       </c>
       <c r="L60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="M60" s="3">
         <v>9300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
-      </c>
-      <c r="T60" s="3">
-        <v>2300</v>
       </c>
       <c r="U60" s="3">
         <v>2300</v>
       </c>
       <c r="V60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="W60" s="3">
         <v>7800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5373,114 +5516,117 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>1500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11100</v>
-      </c>
-      <c r="N61" s="3">
-        <v>12300</v>
       </c>
       <c r="O61" s="3">
         <v>12300</v>
       </c>
       <c r="P61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="Q61" s="3">
         <v>12400</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>12700</v>
       </c>
       <c r="R61" s="3">
         <v>12700</v>
       </c>
       <c r="S61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="T61" s="3">
         <v>11500</v>
-      </c>
-      <c r="T61" s="3">
-        <v>12200</v>
       </c>
       <c r="U61" s="3">
         <v>12200</v>
       </c>
       <c r="V61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="W61" s="3">
         <v>7000</v>
       </c>
       <c r="X61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>8300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>18300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>19400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E62" s="3">
         <v>42900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>44700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>39400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>33100</v>
       </c>
       <c r="J62" s="3">
         <v>33100</v>
@@ -5489,76 +5635,79 @@
         <v>33100</v>
       </c>
       <c r="L62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="M62" s="3">
         <v>36200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>36200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>31400</v>
-      </c>
-      <c r="R62" s="3">
-        <v>31800</v>
       </c>
       <c r="S62" s="3">
         <v>31800</v>
       </c>
       <c r="T62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="U62" s="3">
         <v>31500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>31600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>31500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>32400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>32100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>31400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>29100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>27200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>27000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>26900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>27100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>26100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E66" s="3">
         <v>48000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53900</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>47700</v>
       </c>
       <c r="R66" s="3">
         <v>47700</v>
       </c>
       <c r="S66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="T66" s="3">
         <v>47300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>45900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>46300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>47100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>49400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>51000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>52700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>54900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>53700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-276000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-269500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-250900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-245400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-228300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-221000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-220300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-215400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-210400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-203100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-203500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-194400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-187500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-180200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-175000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-171300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-169000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-165400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-167500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-163300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-161300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-157000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-155300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E76" s="3">
         <v>76900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>73200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>96600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>66500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>66600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>65200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>69400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>51900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>39000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>41000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>44300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>42000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>46000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>51800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>53400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>48400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>45500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>38800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>41900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>44700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>43100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,19 +7400,20 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
@@ -7223,10 +7422,10 @@
         <v>800</v>
       </c>
       <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
@@ -7235,7 +7434,7 @@
         <v>800</v>
       </c>
       <c r="M83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N83" s="3">
         <v>1000</v>
@@ -7250,7 +7449,7 @@
         <v>1000</v>
       </c>
       <c r="R83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="S83" s="3">
         <v>1100</v>
@@ -7271,7 +7470,7 @@
         <v>1100</v>
       </c>
       <c r="Y83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="Z83" s="3">
         <v>900</v>
@@ -7283,10 +7482,10 @@
         <v>900</v>
       </c>
       <c r="AC83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>1300</v>
       </c>
       <c r="AE83" s="3">
         <v>1300</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,52 +8144,53 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>10</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -8017,13 +8238,16 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,44 +8445,47 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -8275,17 +8505,17 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -8293,31 +8523,34 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>3500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,62 +8987,65 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E100" s="3">
         <v>9600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>42700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>16500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>15400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -8807,43 +9053,46 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8866,13 +9115,13 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8890,11 +9139,11 @@
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
@@ -8911,11 +9160,11 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
@@ -8938,104 +9187,110 @@
         <v>0</v>
       </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1500</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,175 +656,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4700</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
         <v>5400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5800</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>6400</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
@@ -853,81 +857,84 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>6900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4800</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
       <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19700</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
       <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
         <v>11700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3300</v>
+        <v>15700</v>
       </c>
       <c r="E9" s="3">
-        <v>1100</v>
+        <v>13400</v>
       </c>
       <c r="F9" s="3">
-        <v>5100</v>
+        <v>12700</v>
       </c>
       <c r="G9" s="3">
-        <v>4900</v>
+        <v>11900</v>
       </c>
       <c r="H9" s="3">
-        <v>3000</v>
+        <v>14200</v>
       </c>
       <c r="I9" s="3">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="J9" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K9" s="3">
         <v>1800</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1700</v>
       </c>
       <c r="L9" s="3">
         <v>1700</v>
@@ -936,99 +943,102 @@
         <v>1700</v>
       </c>
       <c r="N9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O9" s="3">
         <v>1800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1400</v>
+        <v>-9300</v>
       </c>
       <c r="E10" s="3">
-        <v>-1100</v>
+        <v>-8800</v>
       </c>
       <c r="F10" s="3">
-        <v>300</v>
+        <v>-12700</v>
       </c>
       <c r="G10" s="3">
-        <v>900</v>
+        <v>-6400</v>
       </c>
       <c r="H10" s="3">
-        <v>-3000</v>
+        <v>-8400</v>
       </c>
       <c r="I10" s="3">
-        <v>-100</v>
+        <v>-6000</v>
       </c>
       <c r="J10" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>-1700</v>
       </c>
       <c r="L10" s="3">
         <v>-1700</v>
@@ -1037,73 +1047,76 @@
         <v>-1700</v>
       </c>
       <c r="N10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O10" s="3">
         <v>-1800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-2400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>11100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>12500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>9900</v>
-      </c>
-      <c r="H12" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>600</v>
       </c>
       <c r="R12" s="3">
         <v>600</v>
       </c>
       <c r="S12" s="3">
+        <v>600</v>
+      </c>
+      <c r="T12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>1100</v>
       </c>
       <c r="AH12" s="3">
         <v>1100</v>
       </c>
       <c r="AI12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1376,18 +1396,18 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1400,14 +1420,14 @@
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
@@ -1424,8 +1444,8 @@
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1433,40 +1453,43 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E17" s="3">
         <v>16100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>14200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10300</v>
-      </c>
       <c r="H18" s="3">
-        <v>-9000</v>
+        <v>-10400</v>
       </c>
       <c r="I18" s="3">
-        <v>-3200</v>
+        <v>-8900</v>
       </c>
       <c r="J18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,91 +1849,92 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4800</v>
+        <v>-2600</v>
       </c>
       <c r="E20" s="3">
-        <v>-2300</v>
+        <v>-4200</v>
       </c>
       <c r="F20" s="3">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="G20" s="3">
-        <v>-6800</v>
+        <v>-2500</v>
       </c>
       <c r="H20" s="3">
-        <v>1700</v>
+        <v>7200</v>
       </c>
       <c r="I20" s="3">
-        <v>2500</v>
+        <v>-1200</v>
       </c>
       <c r="J20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>300</v>
       </c>
       <c r="V20" s="3">
         <v>300</v>
       </c>
       <c r="W20" s="3">
+        <v>300</v>
+      </c>
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>3500</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>-100</v>
@@ -1912,114 +1946,120 @@
         <v>-100</v>
       </c>
       <c r="AH20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5900</v>
+        <v>-8100</v>
       </c>
       <c r="E21" s="3">
-        <v>-17900</v>
+        <v>-6300</v>
       </c>
       <c r="F21" s="3">
-        <v>-4900</v>
+        <v>-18300</v>
       </c>
       <c r="G21" s="3">
-        <v>-16400</v>
+        <v>-5100</v>
       </c>
       <c r="H21" s="3">
-        <v>-6500</v>
+        <v>-16700</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>-6800</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2041,14 +2081,14 @@
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>200</v>
@@ -2075,10 +2115,10 @@
         <v>200</v>
       </c>
       <c r="U22" s="3">
+        <v>200</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
-      </c>
-      <c r="V22" s="3">
-        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
@@ -2096,7 +2136,7 @@
         <v>200</v>
       </c>
       <c r="AB22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>300</v>
@@ -2108,7 +2148,7 @@
         <v>300</v>
       </c>
       <c r="AF22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AG22" s="3">
         <v>400</v>
@@ -2117,134 +2157,140 @@
         <v>400</v>
       </c>
       <c r="AI22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2297,17 +2343,17 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>10</v>
+      <c r="AB24" s="3">
+        <v>0</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>10</v>
+      <c r="AD24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>10</v>
@@ -2315,14 +2361,17 @@
       <c r="AG24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AH24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,91 +3095,94 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4800</v>
+        <v>2600</v>
       </c>
       <c r="E32" s="3">
-        <v>2300</v>
+        <v>4200</v>
       </c>
       <c r="F32" s="3">
-        <v>-3000</v>
+        <v>-2700</v>
       </c>
       <c r="G32" s="3">
-        <v>6800</v>
+        <v>2500</v>
       </c>
       <c r="H32" s="3">
-        <v>-1700</v>
+        <v>-7200</v>
       </c>
       <c r="I32" s="3">
-        <v>-2500</v>
+        <v>1200</v>
       </c>
       <c r="J32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-300</v>
       </c>
       <c r="V32" s="3">
         <v>-300</v>
       </c>
       <c r="W32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>100</v>
@@ -3124,114 +3194,120 @@
         <v>100</v>
       </c>
       <c r="AH32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E41" s="3">
         <v>61300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>53900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>54600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>77300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>21500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3766,39 +3856,39 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V42" s="3">
         <v>1900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>10200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1300</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
       <c r="AE42" s="3">
         <v>0</v>
       </c>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3823,17 +3916,17 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>5600</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
@@ -3877,11 +3970,11 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
         <v>1100</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
@@ -3895,17 +3988,17 @@
         <v>0</v>
       </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
         <v>7900</v>
       </c>
-      <c r="AF43" s="3">
-        <v>0</v>
-      </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
@@ -3913,43 +4006,46 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E44" s="3">
         <v>5100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4700</v>
-      </c>
-      <c r="H44" s="3">
-        <v>6300</v>
       </c>
       <c r="I44" s="3">
         <v>6300</v>
       </c>
       <c r="J44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="K44" s="3">
         <v>9900</v>
       </c>
       <c r="L44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="M44" s="3">
         <v>7900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>10</v>
       </c>
@@ -3965,272 +4061,281 @@
       <c r="R44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T44" s="3">
         <v>7600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>300</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
       <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
         <v>7100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1800</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
       <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
         <v>7000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>7500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1100</v>
       </c>
       <c r="X45" s="3">
         <v>1100</v>
       </c>
       <c r="Y45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="Z45" s="3">
         <v>800</v>
       </c>
       <c r="AA45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E46" s="3">
         <v>68000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>63700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>84800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>43900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>53900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>200</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -4250,8 +4355,8 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4286,11 +4391,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>7500</v>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA47" s="3">
         <v>7500</v>
@@ -4302,7 +4407,7 @@
         <v>7500</v>
       </c>
       <c r="AD47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AE47" s="3">
         <v>7600</v>
@@ -4319,132 +4424,138 @@
       <c r="AI47" s="3">
         <v>7600</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>61200</v>
+        <v>64700</v>
       </c>
       <c r="E48" s="3">
-        <v>56100</v>
+        <v>61100</v>
       </c>
       <c r="F48" s="3">
         <v>56000</v>
       </c>
       <c r="G48" s="3">
+        <v>55800</v>
+      </c>
+      <c r="H48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="I48" s="3">
+        <v>55700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K48" s="3">
+        <v>55800</v>
+      </c>
+      <c r="L48" s="3">
         <v>56100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="M48" s="3">
+        <v>54900</v>
+      </c>
+      <c r="N48" s="3">
+        <v>55600</v>
+      </c>
+      <c r="O48" s="3">
+        <v>56300</v>
+      </c>
+      <c r="P48" s="3">
         <v>55800</v>
       </c>
-      <c r="I48" s="3">
-        <v>56100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>55800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>56100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>54900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>55600</v>
-      </c>
-      <c r="N48" s="3">
-        <v>56300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>55800</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>56800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>60100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>61100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>63500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>64800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>65800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>66800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>67800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>68900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>69900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>71000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>69000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>69900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>70800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>71600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>72700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>74300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>75200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>75900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,89 +4840,92 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E52" s="3">
         <v>10800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>8100</v>
       </c>
       <c r="K52" s="3">
         <v>8100</v>
       </c>
       <c r="L52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="M52" s="3">
         <v>8000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>15900</v>
       </c>
       <c r="N52" s="3">
         <v>15900</v>
       </c>
       <c r="O52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="P52" s="3">
         <v>15800</v>
       </c>
       <c r="Q52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="R52" s="3">
         <v>15700</v>
       </c>
       <c r="S52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="T52" s="3">
         <v>7900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9800</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E54" s="3">
         <v>140600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>124900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>128400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>131100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>139600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>149100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>94000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>81800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>86600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>86300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>86900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>90400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>88200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>97100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>100400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>101300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>95600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>95400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>88400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>92800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>97400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>98000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>89900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,70 +5230,71 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1400</v>
       </c>
       <c r="M57" s="3">
         <v>1400</v>
       </c>
       <c r="N57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>400</v>
       </c>
       <c r="S57" s="3">
+        <v>400</v>
+      </c>
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
-      </c>
-      <c r="W57" s="3">
-        <v>600</v>
       </c>
       <c r="X57" s="3">
         <v>600</v>
@@ -5175,96 +5306,99 @@
         <v>600</v>
       </c>
       <c r="AA57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H58" s="3">
         <v>5700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1300</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>500</v>
       </c>
       <c r="S58" s="3">
         <v>500</v>
       </c>
       <c r="T58" s="3">
+        <v>500</v>
+      </c>
+      <c r="U58" s="3">
         <v>1700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>5200</v>
@@ -5273,363 +5407,375 @@
         <v>5200</v>
       </c>
       <c r="Z58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AA58" s="3">
         <v>5100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>4800</v>
       </c>
       <c r="AD58" s="3">
         <v>4800</v>
       </c>
       <c r="AE58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>4600</v>
       </c>
       <c r="AG58" s="3">
         <v>4600</v>
       </c>
       <c r="AH58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AI58" s="3">
         <v>4500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="K59" s="3">
+        <v>600</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>5400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>6200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>5100</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1700</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1800</v>
       </c>
       <c r="V59" s="3">
         <v>1800</v>
       </c>
       <c r="W59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="X59" s="3">
         <v>1900</v>
       </c>
       <c r="Y59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z59" s="3">
         <v>3100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
-      </c>
-      <c r="K60" s="3">
-        <v>8600</v>
       </c>
       <c r="L60" s="3">
         <v>8600</v>
       </c>
       <c r="M60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="N60" s="3">
         <v>9300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
-      </c>
-      <c r="U60" s="3">
-        <v>2300</v>
       </c>
       <c r="V60" s="3">
         <v>2300</v>
       </c>
       <c r="W60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="X60" s="3">
         <v>7800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="H61" s="3">
-        <v>2900</v>
+        <v>2000</v>
       </c>
       <c r="I61" s="3">
-        <v>4300</v>
+        <v>3200</v>
       </c>
       <c r="J61" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K61" s="3">
         <v>5700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11100</v>
-      </c>
-      <c r="O61" s="3">
-        <v>12300</v>
       </c>
       <c r="P61" s="3">
         <v>12300</v>
       </c>
       <c r="Q61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="R61" s="3">
         <v>12400</v>
-      </c>
-      <c r="R61" s="3">
-        <v>12700</v>
       </c>
       <c r="S61" s="3">
         <v>12700</v>
       </c>
       <c r="T61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="U61" s="3">
         <v>11500</v>
-      </c>
-      <c r="U61" s="3">
-        <v>12200</v>
       </c>
       <c r="V61" s="3">
         <v>12200</v>
       </c>
       <c r="W61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="X61" s="3">
         <v>7000</v>
       </c>
       <c r="Y61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>8300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>12200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>18300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>19400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>43500</v>
+        <v>40100</v>
       </c>
       <c r="E62" s="3">
-        <v>42900</v>
+        <v>42700</v>
       </c>
       <c r="F62" s="3">
-        <v>43500</v>
+        <v>42300</v>
       </c>
       <c r="G62" s="3">
-        <v>44700</v>
+        <v>42800</v>
       </c>
       <c r="H62" s="3">
-        <v>39200</v>
+        <v>44200</v>
       </c>
       <c r="I62" s="3">
-        <v>39400</v>
+        <v>38900</v>
       </c>
       <c r="J62" s="3">
-        <v>33100</v>
+        <v>39100</v>
       </c>
       <c r="K62" s="3">
         <v>33100</v>
@@ -5638,76 +5784,79 @@
         <v>33100</v>
       </c>
       <c r="M62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="N62" s="3">
         <v>36200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>36200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>31400</v>
-      </c>
-      <c r="S62" s="3">
-        <v>31800</v>
       </c>
       <c r="T62" s="3">
         <v>31800</v>
       </c>
       <c r="U62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="V62" s="3">
         <v>31500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>31600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>31500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>32400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>32100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>31400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>29100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>27300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>27200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>27000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>27100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>26800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>26100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E66" s="3">
         <v>47800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53900</v>
-      </c>
-      <c r="R66" s="3">
-        <v>47700</v>
       </c>
       <c r="S66" s="3">
         <v>47700</v>
       </c>
       <c r="T66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="U66" s="3">
         <v>47300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>46100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>46300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>49400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>47100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>49600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>51000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>52700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>54900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>53700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-276000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-269500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-250900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-245400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-228300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-221000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-220300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-215400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-210000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-203100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-203500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-194400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-187500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-180200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-175000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-171300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-169000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-165400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-167500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-163300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-161300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-157000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-155300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>152900</v>
+      </c>
+      <c r="E76" s="3">
         <v>92800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>76900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>73200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>96600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>62500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>66500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>65200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>69400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>51900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>38900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>39000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>41000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>44300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>42000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>51800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>53400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>48400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>45500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>38800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>41900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>44700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>43100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>36200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,22 +7599,23 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
+        <v>800</v>
+      </c>
+      <c r="G83" s="3">
         <v>700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -7425,10 +7624,10 @@
         <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>800</v>
       </c>
       <c r="L83" s="3">
         <v>800</v>
@@ -7437,7 +7636,7 @@
         <v>800</v>
       </c>
       <c r="N83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="O83" s="3">
         <v>1000</v>
@@ -7452,7 +7651,7 @@
         <v>1000</v>
       </c>
       <c r="S83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="T83" s="3">
         <v>1100</v>
@@ -7473,7 +7672,7 @@
         <v>1100</v>
       </c>
       <c r="Z83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="AA83" s="3">
         <v>900</v>
@@ -7485,10 +7684,10 @@
         <v>900</v>
       </c>
       <c r="AD83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>1300</v>
       </c>
       <c r="AF83" s="3">
         <v>1300</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>1300</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>1300</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,55 +8365,56 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>10</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -8241,13 +8462,16 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,47 +8675,50 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -8508,17 +8738,17 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -8526,31 +8756,34 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>3500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,65 +9233,68 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E100" s="3">
         <v>21800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>42700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>16500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>15300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -9056,43 +9302,46 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9102,29 +9351,29 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9142,11 +9391,11 @@
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -9163,11 +9412,11 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -9190,107 +9439,113 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E102" s="3">
         <v>9500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>44400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1500</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-2200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,185 +656,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F8" s="3">
         <v>6400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4700</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
         <v>5400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5800</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>6400</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -860,93 +867,99 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>6900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>10800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>11500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4800</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
         <v>3800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>19700</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
         <v>11700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>14800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>42400</v>
+      </c>
+      <c r="F9" s="3">
         <v>15700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>13400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>11900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>14200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>7700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1800</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1700</v>
       </c>
       <c r="N9" s="3">
         <v>1700</v>
       </c>
       <c r="O9" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="P9" s="3">
         <v>1700</v>
@@ -958,99 +971,105 @@
         <v>1700</v>
       </c>
       <c r="S9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U9" s="3">
         <v>1500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1800</v>
-      </c>
-      <c r="U9" s="3">
-        <v>6500</v>
-      </c>
-      <c r="V9" s="3">
-        <v>3100</v>
       </c>
       <c r="W9" s="3">
         <v>6500</v>
       </c>
       <c r="X9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Z9" s="3">
         <v>7500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>11200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>5100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>9800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>11200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>6600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>6300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="F10" s="3">
         <v>-9300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-8800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-12700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-6400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-8400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-6000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L10" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>-1700</v>
       </c>
       <c r="N10" s="3">
         <v>-1700</v>
       </c>
       <c r="O10" s="3">
-        <v>-1800</v>
+        <v>-1700</v>
       </c>
       <c r="P10" s="3">
         <v>-1700</v>
@@ -1062,61 +1081,67 @@
         <v>-1700</v>
       </c>
       <c r="S10" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="U10" s="3">
         <v>-1500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-1800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-1700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>4300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>-300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>-200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>9900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>5200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>8500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1178,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1179,86 +1206,92 @@
       <c r="J12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>2000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>2500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,8 +1394,14 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,21 +1438,21 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-900</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1423,17 +1462,17 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
@@ -1447,17 +1486,17 @@
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1465,37 +1504,43 @@
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>900</v>
       </c>
       <c r="J15" s="3">
         <v>900</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1569,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>46200</v>
+      </c>
+      <c r="F17" s="3">
         <v>18300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>16100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>16300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>13800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>16100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5100</v>
-      </c>
-      <c r="L17" s="3">
-        <v>4600</v>
       </c>
       <c r="M17" s="3">
         <v>5100</v>
       </c>
       <c r="N17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>3700</v>
-      </c>
-      <c r="R17" s="3">
-        <v>3500</v>
       </c>
       <c r="S17" s="3">
         <v>3700</v>
       </c>
       <c r="T17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="V17" s="3">
         <v>4000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>8800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>10100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>13200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>8400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>13000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>14200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>10100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>9100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-11900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-11400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-16300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-10400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-8900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4600</v>
       </c>
       <c r="M18" s="3">
         <v>-5100</v>
       </c>
       <c r="N18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-5000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-3500</v>
       </c>
       <c r="S18" s="3">
         <v>-3700</v>
       </c>
       <c r="T18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="V18" s="3">
         <v>-4000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>6700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>5700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,97 +1915,99 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>7200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>3500</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>-100</v>
@@ -1949,122 +2016,134 @@
         <v>-100</v>
       </c>
       <c r="AI20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-8100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-6300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-18300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-5100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-16700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-6000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-6200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>7600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>2900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>6900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>300</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
@@ -2075,8 +2154,8 @@
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
+      <c r="H22" s="3">
+        <v>100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
@@ -2084,17 +2163,17 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
@@ -2118,13 +2197,13 @@
         <v>200</v>
       </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -2139,10 +2218,10 @@
         <v>200</v>
       </c>
       <c r="AC22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>300</v>
@@ -2151,123 +2230,135 @@
         <v>300</v>
       </c>
       <c r="AG22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AH22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AI22" s="3">
         <v>400</v>
       </c>
       <c r="AJ22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-18500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-17200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-7400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>6400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>5200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,11 +2383,11 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2346,32 +2437,38 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>10</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
+      <c r="AI24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ24" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-18500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-17200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-7400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>6400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>5200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-6600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-18500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-17200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-7400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>6400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>5200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,97 +3231,103 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-7200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>100</v>
-      </c>
       <c r="AF32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>100</v>
@@ -3197,117 +3336,129 @@
         <v>100</v>
       </c>
       <c r="AI32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-6600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-18500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-17200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>6400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>5200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-6600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-18500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-17200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>6400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>5200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>76100</v>
+      </c>
+      <c r="F41" s="3">
         <v>118500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>61300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>53900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>59700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>54600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>68000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>77300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>33000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>39900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>43300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>46300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>46200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>33400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>21500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>17600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>5600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>7900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>7300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>8400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3859,42 +4038,42 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>10</v>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X42" s="3">
         <v>1900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>2000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>10200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>2600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1300</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>0</v>
-      </c>
       <c r="AG42" s="3">
         <v>0</v>
       </c>
@@ -3907,32 +4086,38 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
@@ -3973,14 +4158,14 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
@@ -3991,67 +4176,73 @@
         <v>0</v>
       </c>
       <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
         <v>100</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
         <v>7900</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>0</v>
-      </c>
       <c r="AI43" s="3">
         <v>0</v>
       </c>
       <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F44" s="3">
         <v>4200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5100</v>
-      </c>
-      <c r="F44" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>2600</v>
       </c>
       <c r="H44" s="3">
         <v>4700</v>
       </c>
       <c r="I44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K44" s="3">
         <v>6300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>9900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>9900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>7900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
@@ -4064,59 +4255,65 @@
       <c r="S44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V44" s="3">
         <v>7600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>7500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>300</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
       <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
         <v>7100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>6200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1800</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
       <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
         <v>7000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>4500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>7500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>5800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,59 +4338,59 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>1000</v>
       </c>
       <c r="AC45" s="3">
         <v>800</v>
@@ -4202,129 +4399,141 @@
         <v>1000</v>
       </c>
       <c r="AE45" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AF45" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AG45" s="3">
         <v>700</v>
       </c>
       <c r="AH45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>115300</v>
+      </c>
+      <c r="F46" s="3">
         <v>125000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>68000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>60000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>63700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>66500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>75500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>84800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>43900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>51200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>53900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>48900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>48600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>36200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>25000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>18200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>15200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>14000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>6600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>5600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>14700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>11000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>9100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>12600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>8300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>17200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>9200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>12600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>15500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>15200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4358,11 +4567,11 @@
       <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4394,14 +4603,14 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>10</v>
+      <c r="Z47" s="3">
+        <v>0</v>
       </c>
       <c r="AA47" s="3">
-        <v>7500</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>7500</v>
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC47" s="3">
         <v>7500</v>
@@ -4410,10 +4619,10 @@
         <v>7500</v>
       </c>
       <c r="AE47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AF47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AG47" s="3">
         <v>7600</v>
@@ -4427,123 +4636,135 @@
       <c r="AJ47" s="3">
         <v>7600</v>
       </c>
+      <c r="AK47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>66700</v>
+      </c>
+      <c r="F48" s="3">
         <v>64700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>61100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>56000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>55800</v>
       </c>
       <c r="H48" s="3">
         <v>56000</v>
       </c>
       <c r="I48" s="3">
-        <v>55700</v>
+        <v>56000</v>
       </c>
       <c r="J48" s="3">
         <v>56000</v>
       </c>
       <c r="K48" s="3">
+        <v>55700</v>
+      </c>
+      <c r="L48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="M48" s="3">
         <v>55800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>56100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>54900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>55600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>56300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>55800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>56800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>60100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>61100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>63500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>64800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>65800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>66800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>67800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>68900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>69900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>71000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>69000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>69900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>70800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>71600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>72700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>74300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>75200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>75900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>100</v>
-      </c>
-      <c r="F49" s="3">
-        <v>100</v>
       </c>
       <c r="G49" s="3">
         <v>100</v>
@@ -4552,16 +4773,16 @@
         <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4635,8 +4856,14 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,95 +5076,101 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F52" s="3">
         <v>10900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>10800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>8600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>8500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>8400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>8200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>8100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>8100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>15900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>15900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>15800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>15800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>15700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>15700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>7900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>14500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>14900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>14800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>9500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>16200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>12900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>12200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>9800</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4947,8 +5186,14 @@
       <c r="AJ52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>194100</v>
+      </c>
+      <c r="F54" s="3">
         <v>201400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>140600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>124900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>128400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>131100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>139600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>149100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>107900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>115300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>116800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>120500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>120800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>107700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>97500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>94000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>81800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>86600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>86300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>86900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>90400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>88200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>93100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>97100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>100400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>101300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>95600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>95400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>88400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>92800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>97400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>98000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>89900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,76 +5490,78 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F57" s="3">
         <v>5700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
-      </c>
-      <c r="X57" s="3">
-        <v>600</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>600</v>
       </c>
       <c r="Z57" s="3">
         <v>600</v>
@@ -5309,138 +5570,150 @@
         <v>600</v>
       </c>
       <c r="AB57" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="AC57" s="3">
         <v>600</v>
       </c>
       <c r="AD57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF57" s="3">
         <v>1100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>800</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>900</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>1100</v>
       </c>
       <c r="AH57" s="3">
         <v>900</v>
       </c>
       <c r="AI57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK57" s="3">
         <v>700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>5200</v>
+      <c r="X58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>5200</v>
       </c>
       <c r="AA58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AC58" s="3">
         <v>5100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>5000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>4900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>4800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>4800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>4700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>4600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>4600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5453,410 +5726,434 @@
       <c r="F59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>3400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>4300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F60" s="3">
         <v>7500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>7800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>7700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>7500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>7900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>7600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>9300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>7900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>8200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>8400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>9800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
         <v>900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>900</v>
+      </c>
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>11100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>12300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>12300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>12400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>12700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>12700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>11500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>12200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>12200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>7000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>7000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>8300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>9600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>10900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>12200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>13400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>14700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>15900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>17100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>18300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>19400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>41100</v>
+      </c>
+      <c r="F62" s="3">
         <v>40100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>42700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>42300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>42800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>44200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>38900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>39100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>33100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>33100</v>
       </c>
       <c r="M62" s="3">
         <v>33100</v>
       </c>
       <c r="N62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="O62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="P62" s="3">
         <v>36200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>34200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>37100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>37800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>36200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>31400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>31800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>31800</v>
-      </c>
-      <c r="V62" s="3">
-        <v>31500</v>
-      </c>
-      <c r="W62" s="3">
-        <v>31600</v>
       </c>
       <c r="X62" s="3">
         <v>31500</v>
       </c>
       <c r="Y62" s="3">
+        <v>31600</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>31500</v>
+      </c>
+      <c r="AA62" s="3">
         <v>32400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>32100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>31400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>29100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>27300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>27200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>27000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>26900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>27100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>26800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>26100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>61300</v>
+      </c>
+      <c r="F66" s="3">
         <v>48500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>47800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>48000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>53500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>57900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>50200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>52500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>45400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>48800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>50100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>55300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>51500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>55800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>55900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>53900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>47700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>47700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>47300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>45900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>46100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>46300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>47100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>49400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>48500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>47900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>47100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>49900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>49600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>51000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>52700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>54900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-315000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-304100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-284000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-276000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-269500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-250900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-245400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-228300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-221000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-220300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-215400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-210400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-210000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-203100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-203500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-194400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-187500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-180200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-175000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-171300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-169000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-165400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-167500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-163300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-161300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-157000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-155300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>132800</v>
+      </c>
+      <c r="F76" s="3">
         <v>152900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>92800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>76900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>74900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>73200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>89400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>96600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>62500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>66500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>66600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>65200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>69400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>51900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>41600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>40100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>34100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>38900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>39000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>41000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>44300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>42000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>46000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>47700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>51800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>53400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>48400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>45500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>38800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>41900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>44700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>43100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-6600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-18500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-17200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>6400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>5200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,49 +7995,51 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
       </c>
       <c r="I83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
       </c>
       <c r="K83" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L83" s="3">
         <v>800</v>
       </c>
       <c r="M83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>800</v>
       </c>
       <c r="O83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="P83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Q83" s="3">
         <v>1000</v>
@@ -7654,10 +8051,10 @@
         <v>1000</v>
       </c>
       <c r="T83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="U83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="V83" s="3">
         <v>1100</v>
@@ -7675,10 +8072,10 @@
         <v>1100</v>
       </c>
       <c r="AA83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="AB83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="AC83" s="3">
         <v>900</v>
@@ -7687,13 +8084,13 @@
         <v>900</v>
       </c>
       <c r="AE83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>1300</v>
       </c>
       <c r="AH83" s="3">
         <v>1300</v>
@@ -7704,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>1300</v>
       </c>
+      <c r="AK83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>1300</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-11300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-14400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-11700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-7300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>4400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>3900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>6400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>6600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8805,10 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8375,19 +8816,19 @@
         <v>-3800</v>
       </c>
       <c r="E91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-500</v>
       </c>
       <c r="J91" s="3">
         <v>-700</v>
@@ -8396,31 +8837,31 @@
         <v>-500</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8465,13 +8906,19 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +9131,14 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8687,19 +9146,19 @@
         <v>-3800</v>
       </c>
       <c r="E94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-500</v>
       </c>
       <c r="J94" s="3">
         <v>-700</v>
@@ -8708,23 +9167,23 @@
         <v>-500</v>
       </c>
       <c r="L94" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8741,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8753,37 +9212,43 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>3500</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
       <c r="AI94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9313,11 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,91 +9721,97 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>600</v>
+      </c>
+      <c r="F100" s="3">
         <v>68000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>21800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>9600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>5600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>42700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>16500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>15300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>7600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>15400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>8200</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-1200</v>
       </c>
       <c r="AE100" s="3">
         <v>-1100</v>
@@ -9332,16 +9823,22 @@
         <v>-1100</v>
       </c>
       <c r="AH100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9351,36 +9848,36 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>10</v>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
@@ -9394,14 +9891,14 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
@@ -9415,14 +9912,14 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -9442,110 +9939,122 @@
         <v>0</v>
       </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="F102" s="3">
         <v>57300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-13200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>44400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-6800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>12900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>11900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>13300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>2600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>5200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>6800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,195 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3">
         <v>22700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4700</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3">
         <v>5400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5800</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>6400</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -873,90 +877,93 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>6900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4800</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
       <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
         <v>3800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>19700</v>
       </c>
-      <c r="AG8" s="3">
-        <v>0</v>
-      </c>
       <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
         <v>11700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E9" s="3">
         <v>12300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1800</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1700</v>
       </c>
       <c r="O9" s="3">
         <v>1700</v>
@@ -965,108 +972,111 @@
         <v>1700</v>
       </c>
       <c r="Q9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R9" s="3">
         <v>1800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-12300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-19700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-9300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-8800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-12700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-6400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-8400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-6000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="N10" s="3">
-        <v>-1700</v>
       </c>
       <c r="O10" s="3">
         <v>-1700</v>
@@ -1075,73 +1085,76 @@
         <v>-1700</v>
       </c>
       <c r="Q10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R10" s="3">
         <v>-1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1212,86 +1226,89 @@
       <c r="L12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
         <v>1900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>600</v>
       </c>
       <c r="U12" s="3">
         <v>600</v>
       </c>
       <c r="V12" s="3">
+        <v>600</v>
+      </c>
+      <c r="W12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AJ12" s="3">
-        <v>1100</v>
       </c>
       <c r="AK12" s="3">
         <v>1100</v>
       </c>
       <c r="AL12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AM12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1444,18 +1464,18 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1468,14 +1488,14 @@
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
@@ -1492,8 +1512,8 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1501,40 +1521,43 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>900</v>
-      </c>
-      <c r="H15" s="3">
-        <v>700</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>900</v>
@@ -1543,7 +1566,7 @@
         <v>900</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,118 +1683,122 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E17" s="3">
         <v>15800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>14200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1776,109 +1806,112 @@
         <v>-15800</v>
       </c>
       <c r="E18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-23500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,100 +1950,101 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
-      </c>
-      <c r="X20" s="3">
-        <v>300</v>
       </c>
       <c r="Y20" s="3">
         <v>300</v>
       </c>
       <c r="Z20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>3500</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
         <v>-100</v>
@@ -2022,131 +2056,137 @@
         <v>-100</v>
       </c>
       <c r="AK20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-4200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
+      <c r="E22" s="3">
+        <v>300</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>10</v>
@@ -2155,11 +2195,11 @@
         <v>10</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
@@ -2169,14 +2209,14 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
@@ -2203,10 +2243,10 @@
         <v>200</v>
       </c>
       <c r="X22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
@@ -2224,7 +2264,7 @@
         <v>200</v>
       </c>
       <c r="AE22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF22" s="3">
         <v>300</v>
@@ -2236,7 +2276,7 @@
         <v>300</v>
       </c>
       <c r="AI22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AJ22" s="3">
         <v>400</v>
@@ -2245,120 +2285,126 @@
         <v>400</v>
       </c>
       <c r="AL22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AM22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,8 +2435,8 @@
       <c r="L24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2443,17 +2489,17 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>10</v>
+      <c r="AE24" s="3">
+        <v>0</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3" t="s">
-        <v>10</v>
+      <c r="AG24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>10</v>
@@ -2461,14 +2507,17 @@
       <c r="AJ24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="3" t="s">
+      <c r="AK24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,100 +3304,103 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-300</v>
       </c>
       <c r="Y32" s="3">
         <v>-300</v>
       </c>
       <c r="Z32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="3">
         <v>100</v>
@@ -3342,123 +3412,129 @@
         <v>100</v>
       </c>
       <c r="AK32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL32" s="3">
         <v>200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E41" s="3">
         <v>74800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>118500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>53900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>54600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>77300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>33400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4044,39 +4134,39 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y42" s="3">
         <v>1900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1300</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
-      </c>
       <c r="AH42" s="3">
         <v>0</v>
       </c>
@@ -4092,35 +4182,38 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16900</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
       </c>
       <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
         <v>5600</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -4164,11 +4257,11 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
@@ -4182,17 +4275,17 @@
         <v>0</v>
       </c>
       <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
         <v>100</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
-      </c>
       <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
         <v>7900</v>
       </c>
-      <c r="AI43" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
@@ -4200,52 +4293,55 @@
         <v>0</v>
       </c>
       <c r="AL43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E44" s="3">
         <v>23500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4700</v>
-      </c>
-      <c r="K44" s="3">
-        <v>6300</v>
       </c>
       <c r="L44" s="3">
         <v>6300</v>
       </c>
       <c r="M44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="N44" s="3">
         <v>9900</v>
       </c>
       <c r="O44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="P44" s="3">
         <v>7900</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>10</v>
       </c>
@@ -4261,59 +4357,62 @@
       <c r="U44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W44" s="3">
         <v>7600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>300</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
       <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
         <v>7100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1800</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
-      </c>
       <c r="AE44" s="3">
         <v>0</v>
       </c>
       <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
         <v>7000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,196 +4443,202 @@
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>1100</v>
       </c>
       <c r="AA45" s="3">
         <v>1100</v>
       </c>
       <c r="AB45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="AC45" s="3">
         <v>800</v>
       </c>
       <c r="AD45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E46" s="3">
         <v>100000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>115300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>125000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>68000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>60000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>63700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>84800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>51200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>53900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>48900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>48600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>15200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4573,8 +4678,8 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4609,11 +4714,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>7500</v>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD47" s="3">
         <v>7500</v>
@@ -4625,7 +4730,7 @@
         <v>7500</v>
       </c>
       <c r="AG47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AH47" s="3">
         <v>7600</v>
@@ -4642,25 +4747,28 @@
       <c r="AL47" s="3">
         <v>7600</v>
       </c>
+      <c r="AM47" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E48" s="3">
         <v>69300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>66700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>64700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>61100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>56000</v>
       </c>
       <c r="I48" s="3">
         <v>56000</v>
@@ -4669,114 +4777,117 @@
         <v>56000</v>
       </c>
       <c r="K48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="L48" s="3">
         <v>55700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>56100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>54900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>55600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>56300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>55800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>56800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>60100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>61100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>63500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>64800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>65800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>66800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>67800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>68900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>69900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>71000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>69000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>69900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>70800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>71600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>72700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>74300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>75200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>75900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>500</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>100</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -4785,7 +4896,7 @@
         <v>100</v>
       </c>
       <c r="M49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,98 +5199,101 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E52" s="3">
         <v>11100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>8100</v>
       </c>
       <c r="N52" s="3">
         <v>8100</v>
       </c>
       <c r="O52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="P52" s="3">
         <v>8000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>15900</v>
       </c>
       <c r="Q52" s="3">
         <v>15900</v>
       </c>
       <c r="R52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="S52" s="3">
         <v>15800</v>
       </c>
       <c r="T52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="U52" s="3">
         <v>15700</v>
       </c>
       <c r="V52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="W52" s="3">
         <v>7900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9800</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>10</v>
       </c>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E54" s="3">
         <v>182900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>194100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>201400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>140600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>124900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>128400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>131100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>139600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>149100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>107900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>115300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>116800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>120500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>120800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>107700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>94000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>81800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>86600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>86300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>86900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>90400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>88200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>93100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>97100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>100400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>101300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>95600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>95400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>88400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>92800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>97400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>98000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>89900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,79 +5622,80 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1400</v>
       </c>
       <c r="P57" s="3">
         <v>1400</v>
       </c>
       <c r="Q57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>400</v>
       </c>
       <c r="U57" s="3">
         <v>400</v>
       </c>
       <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>600</v>
       </c>
       <c r="AA57" s="3">
         <v>600</v>
@@ -5576,105 +5707,108 @@
         <v>600</v>
       </c>
       <c r="AD57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E58" s="3">
         <v>12700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
       <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
         <v>5900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1300</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>800</v>
-      </c>
-      <c r="U58" s="3">
-        <v>500</v>
       </c>
       <c r="V58" s="3">
         <v>500</v>
       </c>
       <c r="W58" s="3">
+        <v>500</v>
+      </c>
+      <c r="X58" s="3">
         <v>1700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>5200</v>
@@ -5683,37 +5817,40 @@
         <v>5200</v>
       </c>
       <c r="AC58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AD58" s="3">
         <v>5100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>4800</v>
       </c>
       <c r="AG58" s="3">
         <v>4800</v>
       </c>
       <c r="AH58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AI58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>4600</v>
       </c>
       <c r="AJ58" s="3">
         <v>4600</v>
       </c>
       <c r="AK58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AL58" s="3">
         <v>4500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5732,350 +5869,359 @@
       <c r="H59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1700</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1800</v>
       </c>
       <c r="Y59" s="3">
         <v>1800</v>
       </c>
       <c r="Z59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="AA59" s="3">
         <v>1900</v>
       </c>
       <c r="AB59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AC59" s="3">
         <v>3100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E60" s="3">
         <v>20700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6600</v>
-      </c>
-      <c r="N60" s="3">
-        <v>8600</v>
       </c>
       <c r="O60" s="3">
         <v>8600</v>
       </c>
       <c r="P60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>9300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4000</v>
-      </c>
-      <c r="X60" s="3">
-        <v>2300</v>
       </c>
       <c r="Y60" s="3">
         <v>2300</v>
       </c>
       <c r="Z60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA60" s="3">
         <v>7800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1100</v>
-      </c>
-      <c r="E61" s="3">
-        <v>900</v>
       </c>
       <c r="F61" s="3">
         <v>900</v>
       </c>
       <c r="G61" s="3">
+        <v>900</v>
+      </c>
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11100</v>
-      </c>
-      <c r="R61" s="3">
-        <v>12300</v>
       </c>
       <c r="S61" s="3">
         <v>12300</v>
       </c>
       <c r="T61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="U61" s="3">
         <v>12400</v>
-      </c>
-      <c r="U61" s="3">
-        <v>12700</v>
       </c>
       <c r="V61" s="3">
         <v>12700</v>
       </c>
       <c r="W61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="X61" s="3">
         <v>11500</v>
-      </c>
-      <c r="X61" s="3">
-        <v>12200</v>
       </c>
       <c r="Y61" s="3">
         <v>12200</v>
       </c>
       <c r="Z61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="AA61" s="3">
         <v>7000</v>
       </c>
       <c r="AB61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>8300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>19400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E62" s="3">
         <v>38000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>41100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>40100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>42700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>39100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>33100</v>
       </c>
       <c r="N62" s="3">
         <v>33100</v>
@@ -6084,76 +6230,79 @@
         <v>33100</v>
       </c>
       <c r="P62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>36200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>37100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>36200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>31400</v>
-      </c>
-      <c r="V62" s="3">
-        <v>31800</v>
       </c>
       <c r="W62" s="3">
         <v>31800</v>
       </c>
       <c r="X62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="Y62" s="3">
         <v>31500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>31600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>31500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>32400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>32100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>31400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>29100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>27300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>27200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>27000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>26900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>26800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>26100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E66" s="3">
         <v>59800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>50100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>53900</v>
-      </c>
-      <c r="U66" s="3">
-        <v>47700</v>
       </c>
       <c r="V66" s="3">
         <v>47700</v>
       </c>
       <c r="W66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="X66" s="3">
         <v>47300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>46100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>46300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>47100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>49900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>51000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>52700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>54900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>53700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-336000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-315000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-304100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-284000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-276000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-269500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-250900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-245400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-228300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-221000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-220300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-215400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-210400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-210000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-203100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-203500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-194400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-187500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-180200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-175000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-171300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-169000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-165400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-167500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-163300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-161300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-157000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-155300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E76" s="3">
         <v>123100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>132800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>152900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>92800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>76900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>73200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>96600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>66600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>65200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>69400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>51900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>34100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>39000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>41000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>44300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>42000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>46000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>47700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>51800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>53400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>48400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>45500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>38800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>41900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>44700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>43100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>36200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,19 +8195,20 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
@@ -8018,10 +8217,10 @@
         <v>800</v>
       </c>
       <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
@@ -8030,10 +8229,10 @@
         <v>800</v>
       </c>
       <c r="M83" s="3">
+        <v>800</v>
+      </c>
+      <c r="N83" s="3">
         <v>700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>800</v>
       </c>
       <c r="O83" s="3">
         <v>800</v>
@@ -8042,7 +8241,7 @@
         <v>800</v>
       </c>
       <c r="Q83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="R83" s="3">
         <v>1000</v>
@@ -8057,7 +8256,7 @@
         <v>1000</v>
       </c>
       <c r="V83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="W83" s="3">
         <v>1100</v>
@@ -8078,7 +8277,7 @@
         <v>1100</v>
       </c>
       <c r="AC83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="AD83" s="3">
         <v>900</v>
@@ -8090,10 +8289,10 @@
         <v>900</v>
       </c>
       <c r="AG83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>1300</v>
       </c>
       <c r="AI83" s="3">
         <v>1300</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>1300</v>
       </c>
+      <c r="AM83" s="3">
+        <v>1300</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E89" s="3">
         <v>2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-39400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>6600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,64 +9027,65 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>10</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8912,13 +9133,16 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,56 +9364,59 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -9206,17 +9436,17 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
@@ -9224,31 +9454,34 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>3500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI94" s="3">
         <v>-100</v>
       </c>
       <c r="AJ94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK94" s="3">
         <v>0</v>
       </c>
       <c r="AL94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,74 +9970,77 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>68000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>42700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>16500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>15300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>15400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -9802,43 +10048,46 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9854,32 +10103,32 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9897,11 +10146,11 @@
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
@@ -9918,11 +10167,11 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
@@ -9945,116 +10194,122 @@
         <v>0</v>
       </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-42300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>57300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>44400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1500</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,209 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E8" s="3">
         <v>6300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10400</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3">
         <v>22700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4700</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="3">
         <v>5400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5800</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>6400</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -887,96 +890,99 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>6900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4800</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
       <c r="AF8" s="3">
         <v>0</v>
       </c>
       <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
         <v>3800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>19700</v>
       </c>
-      <c r="AI8" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3">
         <v>11700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>14800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E9" s="3">
         <v>21400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>42400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1800</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1700</v>
       </c>
       <c r="Q9" s="3">
         <v>1700</v>
@@ -985,114 +991,117 @@
         <v>1700</v>
       </c>
       <c r="S9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T9" s="3">
         <v>1800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-15100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-12100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-12300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-19700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-9300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-8800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-12700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-6400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-8400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-6000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="P10" s="3">
-        <v>-1700</v>
       </c>
       <c r="Q10" s="3">
         <v>-1700</v>
@@ -1101,73 +1110,76 @@
         <v>-1700</v>
       </c>
       <c r="S10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="T10" s="3">
         <v>-1800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-1500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1246,86 +1259,89 @@
       <c r="N12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1000</v>
-      </c>
-      <c r="V12" s="3">
-        <v>600</v>
       </c>
       <c r="W12" s="3">
         <v>600</v>
       </c>
       <c r="X12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y12" s="3">
         <v>800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AL12" s="3">
-        <v>1100</v>
       </c>
       <c r="AM12" s="3">
         <v>1100</v>
       </c>
       <c r="AN12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AO12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1490,18 +1509,18 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1514,14 +1533,14 @@
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
@@ -1538,8 +1557,8 @@
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1547,17 +1566,20 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1565,28 +1587,28 @@
         <v>2100</v>
       </c>
       <c r="E15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F15" s="3">
         <v>1500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
       <c r="L15" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>900</v>
@@ -1595,7 +1617,7 @@
         <v>900</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E17" s="3">
         <v>26100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>14200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>10100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-19800</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-15800</v>
       </c>
       <c r="F18" s="3">
         <v>-15800</v>
       </c>
       <c r="G18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-23500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>5700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,106 +2017,107 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>7800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>300</v>
       </c>
       <c r="AA20" s="3">
         <v>300</v>
       </c>
       <c r="AB20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>3500</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="3">
         <v>-100</v>
@@ -2096,156 +2129,162 @@
         <v>-100</v>
       </c>
       <c r="AM20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-25600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-19900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6800</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-4200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>6900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="3">
+        <v>300</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
@@ -2255,14 +2294,14 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
@@ -2289,10 +2328,10 @@
         <v>200</v>
       </c>
       <c r="Z22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>200</v>
       </c>
       <c r="AB22" s="3">
         <v>200</v>
@@ -2310,7 +2349,7 @@
         <v>200</v>
       </c>
       <c r="AG22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AH22" s="3">
         <v>300</v>
@@ -2322,7 +2361,7 @@
         <v>300</v>
       </c>
       <c r="AK22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AL22" s="3">
         <v>400</v>
@@ -2331,126 +2370,132 @@
         <v>400</v>
       </c>
       <c r="AN22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AO22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,8 +2532,8 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2541,17 +2586,17 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>10</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="3" t="s">
-        <v>10</v>
+      <c r="AI24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="s">
         <v>10</v>
@@ -2559,14 +2604,17 @@
       <c r="AL24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AM24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>5200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,106 +3443,109 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-300</v>
       </c>
       <c r="AA32" s="3">
         <v>-300</v>
       </c>
       <c r="AB32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="3">
         <v>100</v>
@@ -3488,129 +3557,135 @@
         <v>100</v>
       </c>
       <c r="AM32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN32" s="3">
         <v>200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>5200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>5200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E41" s="3">
         <v>52000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>76100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>118500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>61300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4230,39 +4319,39 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA42" s="3">
         <v>1900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1300</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
@@ -4278,41 +4367,44 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
       </c>
       <c r="L43" s="3">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3">
         <v>5600</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4356,11 +4448,11 @@
         <v>0</v>
       </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>1100</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
@@ -4374,17 +4466,17 @@
         <v>0</v>
       </c>
       <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
         <v>100</v>
       </c>
-      <c r="AI43" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
         <v>7900</v>
       </c>
-      <c r="AK43" s="3">
-        <v>0</v>
-      </c>
       <c r="AL43" s="3">
         <v>0</v>
       </c>
@@ -4392,58 +4484,61 @@
         <v>0</v>
       </c>
       <c r="AN43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E44" s="3">
         <v>19200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>20700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4700</v>
-      </c>
-      <c r="M44" s="3">
-        <v>6300</v>
       </c>
       <c r="N44" s="3">
         <v>6300</v>
       </c>
       <c r="O44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="P44" s="3">
         <v>9900</v>
       </c>
       <c r="Q44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="R44" s="3">
         <v>7900</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>10</v>
       </c>
@@ -4459,59 +4554,62 @@
       <c r="W44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y44" s="3">
         <v>7600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>300</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
       <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
         <v>7100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1800</v>
       </c>
-      <c r="AF44" s="3">
-        <v>0</v>
-      </c>
       <c r="AG44" s="3">
         <v>0</v>
       </c>
       <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
         <v>7000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>7500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,202 +4646,208 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>900</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>1100</v>
       </c>
       <c r="AC45" s="3">
         <v>1100</v>
       </c>
       <c r="AD45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="AE45" s="3">
         <v>800</v>
       </c>
       <c r="AF45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG45" s="3">
         <v>1000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>150400</v>
+      </c>
+      <c r="E46" s="3">
         <v>76600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>81000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>100000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>115300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>125000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>68000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>60000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>66500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>84800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>51200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>53900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>48900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>48600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>25000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>15500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4789,8 +4893,8 @@
       <c r="Q47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4825,11 +4929,11 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>7500</v>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF47" s="3">
         <v>7500</v>
@@ -4841,7 +4945,7 @@
         <v>7500</v>
       </c>
       <c r="AI47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AJ47" s="3">
         <v>7600</v>
@@ -4858,31 +4962,34 @@
       <c r="AN47" s="3">
         <v>7600</v>
       </c>
+      <c r="AO47" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E48" s="3">
         <v>80900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>76900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>64700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>56000</v>
       </c>
       <c r="K48" s="3">
         <v>56000</v>
@@ -4891,91 +4998,94 @@
         <v>56000</v>
       </c>
       <c r="M48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="N48" s="3">
         <v>55700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>56000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>55800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>56100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>55600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>56300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>55800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>56800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>60100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>61100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>63500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>64800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>65800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>66800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>67800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>68900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>69900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>71000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>69000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>69900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>70800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>71600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>72700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>74300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>75200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>75900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4986,25 +5096,25 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>100</v>
       </c>
       <c r="J49" s="3">
         <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M49" s="3">
         <v>100</v>
@@ -5013,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="O49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,104 +5438,107 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E52" s="3">
         <v>11400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>8100</v>
       </c>
       <c r="P52" s="3">
         <v>8100</v>
       </c>
       <c r="Q52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="R52" s="3">
         <v>8000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>15900</v>
       </c>
       <c r="S52" s="3">
         <v>15900</v>
       </c>
       <c r="T52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="U52" s="3">
         <v>15800</v>
       </c>
       <c r="V52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="W52" s="3">
         <v>15700</v>
       </c>
       <c r="X52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Y52" s="3">
         <v>7900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9800</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>10</v>
       </c>
@@ -5438,8 +5557,11 @@
       <c r="AN52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>272500</v>
+      </c>
+      <c r="E54" s="3">
         <v>170900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>171300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>182900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>194100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>201400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>140600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>124900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>128400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>131100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>139600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>116800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>120500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>107700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>97500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>94000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>81800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>86600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>86300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>86900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>90400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>88200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>93100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>97100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>100400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>101300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>95600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>95400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>88400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>92800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>97400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>98000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>89900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,85 +5883,86 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1400</v>
       </c>
       <c r="R57" s="3">
         <v>1400</v>
       </c>
       <c r="S57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
-      </c>
-      <c r="V57" s="3">
-        <v>400</v>
       </c>
       <c r="W57" s="3">
         <v>400</v>
       </c>
       <c r="X57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>600</v>
       </c>
       <c r="AC57" s="3">
         <v>600</v>
@@ -5844,111 +5974,114 @@
         <v>600</v>
       </c>
       <c r="AF57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG57" s="3">
         <v>900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
       </c>
       <c r="K58" s="3">
+        <v>200</v>
+      </c>
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1300</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>800</v>
-      </c>
-      <c r="W58" s="3">
-        <v>500</v>
       </c>
       <c r="X58" s="3">
         <v>500</v>
       </c>
       <c r="Y58" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1700</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>5200</v>
@@ -5957,37 +6090,40 @@
         <v>5200</v>
       </c>
       <c r="AE58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AF58" s="3">
         <v>5100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>4800</v>
       </c>
       <c r="AI58" s="3">
         <v>4800</v>
       </c>
       <c r="AJ58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AK58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>4600</v>
       </c>
       <c r="AL58" s="3">
         <v>4600</v>
       </c>
       <c r="AM58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AN58" s="3">
         <v>4500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6012,368 +6148,377 @@
       <c r="J59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1700</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1800</v>
       </c>
       <c r="AA59" s="3">
         <v>1800</v>
       </c>
       <c r="AB59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="AC59" s="3">
         <v>1900</v>
       </c>
       <c r="AD59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE59" s="3">
         <v>3100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E60" s="3">
         <v>9800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6600</v>
-      </c>
-      <c r="P60" s="3">
-        <v>8600</v>
       </c>
       <c r="Q60" s="3">
         <v>8600</v>
       </c>
       <c r="R60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="S60" s="3">
         <v>9300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>2300</v>
       </c>
       <c r="AA60" s="3">
         <v>2300</v>
       </c>
       <c r="AB60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AC60" s="3">
         <v>7800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>9800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E61" s="3">
         <v>18300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>900</v>
       </c>
       <c r="H61" s="3">
         <v>900</v>
       </c>
       <c r="I61" s="3">
+        <v>900</v>
+      </c>
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11100</v>
-      </c>
-      <c r="T61" s="3">
-        <v>12300</v>
       </c>
       <c r="U61" s="3">
         <v>12300</v>
       </c>
       <c r="V61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="W61" s="3">
         <v>12400</v>
-      </c>
-      <c r="W61" s="3">
-        <v>12700</v>
       </c>
       <c r="X61" s="3">
         <v>12700</v>
       </c>
       <c r="Y61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="Z61" s="3">
         <v>11500</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>12200</v>
       </c>
       <c r="AA61" s="3">
         <v>12200</v>
       </c>
       <c r="AB61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="AC61" s="3">
         <v>7000</v>
       </c>
       <c r="AD61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>8300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>15900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>17100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>19400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E62" s="3">
         <v>52200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39100</v>
-      </c>
-      <c r="O62" s="3">
-        <v>33100</v>
       </c>
       <c r="P62" s="3">
         <v>33100</v>
@@ -6382,76 +6527,79 @@
         <v>33100</v>
       </c>
       <c r="R62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="S62" s="3">
         <v>36200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>34200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>37100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>36200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>31400</v>
-      </c>
-      <c r="X62" s="3">
-        <v>31800</v>
       </c>
       <c r="Y62" s="3">
         <v>31800</v>
       </c>
       <c r="Z62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="AA62" s="3">
         <v>31500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>31600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>31500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>32400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>32100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>31400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>29100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>27300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>27200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>26900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>27100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>26800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>26100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E66" s="3">
         <v>80300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>53900</v>
-      </c>
-      <c r="W66" s="3">
-        <v>47700</v>
       </c>
       <c r="X66" s="3">
         <v>47700</v>
       </c>
       <c r="Y66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="Z66" s="3">
         <v>47300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>47100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>49400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>48500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>47900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>47100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>49900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>49600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>51000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>52700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>54900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>53700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-379000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-363400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-336000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-315000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-304100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-284000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-276000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-269500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-250900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-245400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-228300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-221000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-220300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-215400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-210400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-210000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-203100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-203500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-194400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-187500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-180200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-175000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-171300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-169000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-165400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-167500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-163300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-161300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-157000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-155300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E76" s="3">
         <v>90700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>102100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>123100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>132800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>152900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>92800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>76900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>73200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>96600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>62500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>66500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>65200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>69400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>51900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>41600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>40100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>38900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>41000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>44300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>42000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>47700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>51800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>48400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>45500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>41900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>44700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>43100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>36200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>5200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8592,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8404,16 +8602,16 @@
         <v>900</v>
       </c>
       <c r="E83" s="3">
+        <v>900</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
       </c>
       <c r="H83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
@@ -8422,10 +8620,10 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>800</v>
       </c>
       <c r="M83" s="3">
         <v>800</v>
@@ -8434,10 +8632,10 @@
         <v>800</v>
       </c>
       <c r="O83" s="3">
+        <v>800</v>
+      </c>
+      <c r="P83" s="3">
         <v>700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>800</v>
       </c>
       <c r="Q83" s="3">
         <v>800</v>
@@ -8446,7 +8644,7 @@
         <v>800</v>
       </c>
       <c r="S83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="T83" s="3">
         <v>1000</v>
@@ -8461,7 +8659,7 @@
         <v>1000</v>
       </c>
       <c r="X83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Y83" s="3">
         <v>1100</v>
@@ -8482,7 +8680,7 @@
         <v>1100</v>
       </c>
       <c r="AE83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="AF83" s="3">
         <v>900</v>
@@ -8494,10 +8692,10 @@
         <v>900</v>
       </c>
       <c r="AI83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>1300</v>
       </c>
       <c r="AK83" s="3">
         <v>1300</v>
@@ -8511,8 +8709,11 @@
       <c r="AN83" s="3">
         <v>1300</v>
       </c>
+      <c r="AO83" s="3">
+        <v>1300</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>6600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,70 +9468,71 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>10</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -9360,13 +9580,16 @@
         <v>0</v>
       </c>
       <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,62 +9823,65 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -9672,17 +9901,17 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
@@ -9690,31 +9919,34 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>3500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK94" s="3">
         <v>-100</v>
       </c>
       <c r="AL94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM94" s="3">
         <v>0</v>
       </c>
       <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10026,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,80 +10461,83 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100100</v>
+      </c>
+      <c r="E100" s="3">
         <v>14900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>68000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>42700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>16500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>15300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>15400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -10300,48 +10545,51 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -10358,32 +10606,32 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>-100</v>
       </c>
       <c r="N101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -10401,11 +10649,11 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -10422,11 +10670,11 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -10449,122 +10697,128 @@
         <v>0</v>
       </c>
       <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-42300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>57300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>44400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1500</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>5200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>6800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>URG</t>
   </si>
@@ -656,215 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E8" s="3">
         <v>10400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10400</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
         <v>22700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4700</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="3">
         <v>5400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5800</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>6400</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -893,99 +897,102 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>6900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4800</v>
       </c>
-      <c r="AF8" s="3">
-        <v>0</v>
-      </c>
       <c r="AG8" s="3">
         <v>0</v>
       </c>
       <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
         <v>3800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ8" s="3">
-        <v>0</v>
-      </c>
       <c r="AK8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3">
         <v>11700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>14800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="3">
         <v>25200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>42400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1700</v>
       </c>
       <c r="R9" s="3">
         <v>1700</v>
@@ -994,117 +1001,120 @@
         <v>1700</v>
       </c>
       <c r="T9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U9" s="3">
         <v>1800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>11200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>6300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>-14800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-15100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-12100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-12300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-19700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-9300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-8800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-12700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-6400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-8400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-6000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>-1700</v>
       </c>
       <c r="R10" s="3">
         <v>-1700</v>
@@ -1113,73 +1123,76 @@
         <v>-1700</v>
       </c>
       <c r="T10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="U10" s="3">
         <v>-1800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-1700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1262,86 +1276,89 @@
       <c r="O12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
-      </c>
-      <c r="W12" s="3">
-        <v>600</v>
       </c>
       <c r="X12" s="3">
         <v>600</v>
       </c>
       <c r="Y12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z12" s="3">
         <v>800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AM12" s="3">
-        <v>1100</v>
       </c>
       <c r="AN12" s="3">
         <v>1100</v>
       </c>
       <c r="AO12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AP12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1512,18 +1532,18 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-900</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1536,14 +1556,14 @@
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1560,8 +1580,8 @@
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
@@ -1569,49 +1589,52 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="E15" s="3">
         <v>2100</v>
       </c>
       <c r="F15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>900</v>
-      </c>
-      <c r="K15" s="3">
-        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
       </c>
       <c r="M15" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>900</v>
@@ -1620,7 +1643,7 @@
         <v>900</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E17" s="3">
         <v>28400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>14200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>10100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>9100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-15800</v>
       </c>
       <c r="G18" s="3">
         <v>-15800</v>
       </c>
       <c r="H18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-23500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>5700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,109 +2051,110 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>300</v>
       </c>
       <c r="AB20" s="3">
         <v>300</v>
       </c>
       <c r="AC20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>3500</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3">
         <v>-100</v>
@@ -2132,162 +2166,168 @@
         <v>-100</v>
       </c>
       <c r="AN20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-25600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6800</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>6900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
       </c>
       <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
@@ -2297,14 +2337,14 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -2331,10 +2371,10 @@
         <v>200</v>
       </c>
       <c r="AA22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
@@ -2352,7 +2392,7 @@
         <v>200</v>
       </c>
       <c r="AH22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AI22" s="3">
         <v>300</v>
@@ -2364,7 +2404,7 @@
         <v>300</v>
       </c>
       <c r="AL22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AM22" s="3">
         <v>400</v>
@@ -2373,129 +2413,135 @@
         <v>400</v>
       </c>
       <c r="AO22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AP22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>5200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2535,8 +2581,8 @@
       <c r="O24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2589,17 +2635,17 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>10</v>
+      <c r="AH24" s="3">
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="s">
-        <v>10</v>
+      <c r="AJ24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0</v>
       </c>
       <c r="AL24" s="3" t="s">
         <v>10</v>
@@ -2607,14 +2653,17 @@
       <c r="AM24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AN24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="3" t="s">
+      <c r="AN24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>5200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>5200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,109 +3513,112 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-300</v>
       </c>
       <c r="AB32" s="3">
         <v>-300</v>
       </c>
       <c r="AC32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3">
         <v>100</v>
@@ -3560,132 +3630,138 @@
         <v>100</v>
       </c>
       <c r="AN32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO32" s="3">
         <v>200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>5200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>5200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,132 +4218,136 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E41" s="3">
         <v>123900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>57600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>118500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>68000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>77300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>39900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4322,39 +4412,39 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB42" s="3">
         <v>1900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
-      </c>
       <c r="AK42" s="3">
         <v>0</v>
       </c>
@@ -4370,8 +4460,11 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4379,35 +4472,35 @@
         <v>700</v>
       </c>
       <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16900</v>
-      </c>
-      <c r="I43" s="3">
-        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>5600</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
@@ -4451,11 +4544,11 @@
         <v>0</v>
       </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>1100</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
@@ -4469,17 +4562,17 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>100</v>
       </c>
-      <c r="AJ43" s="3">
-        <v>0</v>
-      </c>
       <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
         <v>7900</v>
       </c>
-      <c r="AL43" s="3">
-        <v>0</v>
-      </c>
       <c r="AM43" s="3">
         <v>0</v>
       </c>
@@ -4487,61 +4580,64 @@
         <v>0</v>
       </c>
       <c r="AO43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E44" s="3">
         <v>24300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4700</v>
-      </c>
-      <c r="N44" s="3">
-        <v>6300</v>
       </c>
       <c r="O44" s="3">
         <v>6300</v>
       </c>
       <c r="P44" s="3">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="Q44" s="3">
         <v>9900</v>
       </c>
       <c r="R44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="S44" s="3">
         <v>7900</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>10</v>
       </c>
@@ -4557,59 +4653,62 @@
       <c r="X44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z44" s="3">
         <v>7600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>300</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
-      </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
       <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
         <v>7100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1800</v>
       </c>
-      <c r="AG44" s="3">
-        <v>0</v>
-      </c>
       <c r="AH44" s="3">
         <v>0</v>
       </c>
       <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>7500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>5800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4649,205 +4748,211 @@
       <c r="O45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>900</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>1100</v>
       </c>
       <c r="AD45" s="3">
         <v>1100</v>
       </c>
       <c r="AE45" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="AF45" s="3">
         <v>800</v>
       </c>
       <c r="AG45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH45" s="3">
         <v>1000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>154100</v>
+      </c>
+      <c r="E46" s="3">
         <v>150400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>76600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>100000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>115300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>125000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>68000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>63700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>66500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>75500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>84800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>51200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>53900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>48900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>48600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>25000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>15200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4896,8 +5001,8 @@
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4932,11 +5037,11 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>7500</v>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG47" s="3">
         <v>7500</v>
@@ -4948,7 +5053,7 @@
         <v>7500</v>
       </c>
       <c r="AJ47" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AK47" s="3">
         <v>7600</v>
@@ -4965,34 +5070,37 @@
       <c r="AO47" s="3">
         <v>7600</v>
       </c>
+      <c r="AP47" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E48" s="3">
         <v>93600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>80900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>76900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>61100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>56000</v>
       </c>
       <c r="L48" s="3">
         <v>56000</v>
@@ -5001,91 +5109,94 @@
         <v>56000</v>
       </c>
       <c r="N48" s="3">
+        <v>56000</v>
+      </c>
+      <c r="O48" s="3">
         <v>55700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>56000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>55800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>56100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>54900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>55600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>56300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>55800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>56800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>60100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>61100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>63500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>64800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>65800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>66800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>67800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>68900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>69900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>71000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>69000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>69900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>70800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>71600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>72700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>74300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>75200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>75900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5099,25 +5210,25 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>100</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>100</v>
@@ -5126,7 +5237,7 @@
         <v>100</v>
       </c>
       <c r="P49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -5203,8 +5314,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,107 +5558,110 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E52" s="3">
         <v>26600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>8100</v>
       </c>
       <c r="Q52" s="3">
         <v>8100</v>
       </c>
       <c r="R52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="S52" s="3">
         <v>8000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>15900</v>
       </c>
       <c r="T52" s="3">
         <v>15900</v>
       </c>
       <c r="U52" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="V52" s="3">
         <v>15800</v>
       </c>
       <c r="W52" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="X52" s="3">
         <v>15700</v>
       </c>
       <c r="Y52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Z52" s="3">
         <v>7900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9800</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>10</v>
       </c>
@@ -5560,8 +5680,11 @@
       <c r="AO52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>291600</v>
+      </c>
+      <c r="E54" s="3">
         <v>272500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>170900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>171300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>182900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>194100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>201400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>140600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>124900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>128400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>131100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>139600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>149100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>107900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>115300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>116800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>107700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>97500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>94000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>81800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>86600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>86300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>86900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>90400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>88200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>93100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>97100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>100400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>101300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>95600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>95400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>88400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>92800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>97400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>98000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>89900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,88 +6014,89 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E57" s="3">
         <v>8600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1400</v>
       </c>
       <c r="S57" s="3">
         <v>1400</v>
       </c>
       <c r="T57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>400</v>
       </c>
       <c r="Y57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>600</v>
       </c>
       <c r="AD57" s="3">
         <v>600</v>
@@ -5977,114 +6108,117 @@
         <v>600</v>
       </c>
       <c r="AG57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH57" s="3">
         <v>900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E58" s="3">
         <v>17100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1300</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>800</v>
-      </c>
-      <c r="X58" s="3">
-        <v>500</v>
       </c>
       <c r="Y58" s="3">
         <v>500</v>
       </c>
       <c r="Z58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1700</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC58" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>5200</v>
@@ -6093,37 +6227,40 @@
         <v>5200</v>
       </c>
       <c r="AF58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AG58" s="3">
         <v>5100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>4800</v>
       </c>
       <c r="AJ58" s="3">
         <v>4800</v>
       </c>
       <c r="AK58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AL58" s="3">
         <v>4700</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>4600</v>
       </c>
       <c r="AM58" s="3">
         <v>4600</v>
       </c>
       <c r="AN58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AO58" s="3">
         <v>4500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6151,377 +6288,386 @@
       <c r="K59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1700</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>1800</v>
       </c>
       <c r="AB59" s="3">
         <v>1800</v>
       </c>
       <c r="AC59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="AD59" s="3">
         <v>1900</v>
       </c>
       <c r="AE59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AF59" s="3">
         <v>3100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E60" s="3">
         <v>27700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6600</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>8600</v>
       </c>
       <c r="R60" s="3">
         <v>8600</v>
       </c>
       <c r="S60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="T60" s="3">
         <v>9300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4000</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>2300</v>
       </c>
       <c r="AB60" s="3">
         <v>2300</v>
       </c>
       <c r="AC60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AD60" s="3">
         <v>7800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>8400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>9800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>8200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E61" s="3">
         <v>67700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>900</v>
       </c>
       <c r="I61" s="3">
         <v>900</v>
       </c>
       <c r="J61" s="3">
+        <v>900</v>
+      </c>
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11100</v>
-      </c>
-      <c r="U61" s="3">
-        <v>12300</v>
       </c>
       <c r="V61" s="3">
         <v>12300</v>
       </c>
       <c r="W61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="X61" s="3">
         <v>12400</v>
-      </c>
-      <c r="X61" s="3">
-        <v>12700</v>
       </c>
       <c r="Y61" s="3">
         <v>12700</v>
       </c>
       <c r="Z61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AA61" s="3">
         <v>11500</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>12200</v>
       </c>
       <c r="AB61" s="3">
         <v>12200</v>
       </c>
       <c r="AC61" s="3">
-        <v>7000</v>
+        <v>12200</v>
       </c>
       <c r="AD61" s="3">
         <v>7000</v>
       </c>
       <c r="AE61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>8300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>15900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>17100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>18300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>19400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E62" s="3">
         <v>99600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>52200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>43900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>39100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>33100</v>
       </c>
       <c r="Q62" s="3">
         <v>33100</v>
@@ -6530,76 +6676,79 @@
         <v>33100</v>
       </c>
       <c r="S62" s="3">
+        <v>33100</v>
+      </c>
+      <c r="T62" s="3">
         <v>36200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>34200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>36200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>31400</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>31800</v>
       </c>
       <c r="Z62" s="3">
         <v>31800</v>
       </c>
       <c r="AA62" s="3">
+        <v>31800</v>
+      </c>
+      <c r="AB62" s="3">
         <v>31500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>31600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>31500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>32400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>32100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>31400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>29100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>27300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>27200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>27000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>26900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>27100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>26800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>26100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>208800</v>
+      </c>
+      <c r="E66" s="3">
         <v>195000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>59800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>50200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>53900</v>
-      </c>
-      <c r="X66" s="3">
-        <v>47700</v>
       </c>
       <c r="Y66" s="3">
         <v>47700</v>
       </c>
       <c r="Z66" s="3">
+        <v>47700</v>
+      </c>
+      <c r="AA66" s="3">
         <v>47300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>46300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>49400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>48500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>47900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>47100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>49900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>49600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>51000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>52700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>54900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>53700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-407800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-379000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-363400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-336000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-315000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-304100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-284000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-276000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-269500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-250900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-245400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-228300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-221000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-220300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-215400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-210400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-210000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-203100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-203500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-194400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-187500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-180200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-175000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-171300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-169000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-165400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-167500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-163300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-161300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-157000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-155300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-151500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-157400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-154000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-152300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-157500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-157600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E76" s="3">
         <v>77500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>102100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>123100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>132800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>152900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>92800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>76900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>74900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>73200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>89400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>96600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>62500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>66600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>65200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>69400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>51900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>41600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>34100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>38900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>39000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>41000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>44300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>42000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>47700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>51800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>53400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>48400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>38800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>41900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>44700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>43100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>36200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>5200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,28 +8791,29 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
         <v>900</v>
       </c>
       <c r="F83" s="3">
+        <v>900</v>
+      </c>
+      <c r="G83" s="3">
         <v>700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
       </c>
       <c r="I83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
@@ -8623,10 +8822,10 @@
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>800</v>
       </c>
       <c r="N83" s="3">
         <v>800</v>
@@ -8635,10 +8834,10 @@
         <v>800</v>
       </c>
       <c r="P83" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>700</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>800</v>
       </c>
       <c r="R83" s="3">
         <v>800</v>
@@ -8647,7 +8846,7 @@
         <v>800</v>
       </c>
       <c r="T83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U83" s="3">
         <v>1000</v>
@@ -8662,7 +8861,7 @@
         <v>1000</v>
       </c>
       <c r="Y83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Z83" s="3">
         <v>1100</v>
@@ -8683,7 +8882,7 @@
         <v>1100</v>
       </c>
       <c r="AF83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="AG83" s="3">
         <v>900</v>
@@ -8695,10 +8894,10 @@
         <v>900</v>
       </c>
       <c r="AJ83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK83" s="3">
         <v>1100</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>1300</v>
       </c>
       <c r="AL83" s="3">
         <v>1300</v>
@@ -8712,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>1300</v>
       </c>
+      <c r="AP83" s="3">
+        <v>1300</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-39400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>6600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,73 +9689,74 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>10</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -9583,13 +9804,16 @@
         <v>0</v>
       </c>
       <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,65 +10053,68 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -9904,17 +10134,17 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
@@ -9922,31 +10152,34 @@
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>3500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
-      </c>
       <c r="AK94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AL94" s="3">
         <v>-100</v>
       </c>
       <c r="AM94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AN94" s="3">
         <v>0</v>
       </c>
       <c r="AO94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10029,8 +10263,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,83 +10707,86 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E100" s="3">
         <v>100100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>68000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>42700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>16500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>15300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>15400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -10548,43 +10794,46 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>8200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10592,7 +10841,7 @@
         <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -10609,32 +10858,32 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
       </c>
       <c r="O101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>-100</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -10652,11 +10901,11 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
@@ -10673,11 +10922,11 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
         <v>0</v>
       </c>
@@ -10700,125 +10949,131 @@
         <v>0</v>
       </c>
       <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>71900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-42300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>57300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1500</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>6800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>500</v>
       </c>
     </row>
